--- a/Deliverables/BOM/LCSC_Control_Board.xlsx
+++ b/Deliverables/BOM/LCSC_Control_Board.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="172">
   <si>
     <t xml:space="preserve">Bill of Material (BOM) for Refrence Formate </t>
   </si>
@@ -106,7 +106,8 @@
     <t>CAP CER 0.1UF 100V X7R 0603</t>
   </si>
   <si>
-    <t>C2, C4, C6, C7, C8, C9, C10, C11, C12, C13, C14, C15, C16, C20, C21, C22, C23, C24, C25, C30, C31, C41</t>
+    <t xml:space="preserve">C2, C4, C6, C7, C8, C9, C10, C11, C12, C13, C14, C15, C16, C20, C21, C22, C23, C24, C25, C30, C31, C34, C35, C41
+</t>
   </si>
   <si>
     <t>Cap0603</t>
@@ -193,7 +194,7 @@
     <t>Green 520~535nm 0402 Light Emitting Diodes (LED) RoHS</t>
   </si>
   <si>
-    <t>LED1, LED2</t>
+    <t>LED1, LED2,LED3</t>
   </si>
   <si>
     <t>LED 0402</t>
@@ -256,7 +257,7 @@
     <t>RES SMD 10K OHM 5% 1/10W 0603</t>
   </si>
   <si>
-    <t>R1, R2, R3, R4, R5, R9, R14, R15, R16, R41, R42,R23</t>
+    <t>R1, R2, R3, R4, R5, R9, R14, R15, R16, R23, R41, R42</t>
   </si>
   <si>
     <t>Res0603</t>
@@ -304,7 +305,7 @@
     <t>RES SMD 1K OHM 1% 1/10W 0603</t>
   </si>
   <si>
-    <t>R8, R10, R40</t>
+    <t>R8, R10, R40,R17</t>
   </si>
   <si>
     <t>RC0603FR-071KL</t>
@@ -316,6 +317,36 @@
     <t>1K</t>
   </si>
   <si>
+    <t>RES SMD 100 OHM 1% 1/10W 0603</t>
+  </si>
+  <si>
+    <t>R18, R19</t>
+  </si>
+  <si>
+    <t>RC0603FR-07100RL</t>
+  </si>
+  <si>
+    <t>C105588</t>
+  </si>
+  <si>
+    <t>100R</t>
+  </si>
+  <si>
+    <t>RES SMD 470 OHM 1% 1/10W 0603</t>
+  </si>
+  <si>
+    <t>R20</t>
+  </si>
+  <si>
+    <t>RC0603FR-07470RL</t>
+  </si>
+  <si>
+    <t>C114669</t>
+  </si>
+  <si>
+    <t>470R</t>
+  </si>
+  <si>
     <t>RES SMD 12.1K OHM 1/10W 0603</t>
   </si>
   <si>
@@ -406,7 +437,7 @@
     <t>IC TRNSLTR BIDIRECTIONAL US8</t>
   </si>
   <si>
-    <t>U5</t>
+    <t>U3</t>
   </si>
   <si>
     <t>8-VSSOP</t>
@@ -454,7 +485,7 @@
     <t xml:space="preserve"> 2.54mm Pin Header Male single row Right Angle SMD</t>
   </si>
   <si>
-    <t>J1</t>
+    <t>J1,J2</t>
   </si>
   <si>
     <t>HDR1X5 SMD</t>
@@ -509,17 +540,18 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
+  <numFmts count="9">
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="178" formatCode="&quot;$&quot;#,##0.0000"/>
     <numFmt numFmtId="179" formatCode="&quot;$&quot;#,##0.00000"/>
-    <numFmt numFmtId="180" formatCode="&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="181" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    <numFmt numFmtId="180" formatCode="&quot;$&quot;#,##0.0000_);[Red]\(&quot;$&quot;#,##0.0000\)"/>
+    <numFmt numFmtId="181" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="182" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
   </numFmts>
-  <fonts count="41">
+  <fonts count="39">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -559,13 +591,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -573,10 +598,15 @@
     </font>
     <font>
       <sz val="10"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <charset val="134"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF333333"/>
+      <name val="Arial"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
@@ -584,12 +614,6 @@
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF333333"/>
-      <name val="Arial"/>
-      <charset val="134"/>
     </font>
     <font>
       <strike/>
@@ -613,22 +637,9 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="10"/>
       <color theme="10"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF333333"/>
       <name val="Calibri"/>
       <charset val="134"/>
     </font>
@@ -639,6 +650,12 @@
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF333333"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -683,10 +700,18 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -704,8 +729,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -713,22 +746,38 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -743,39 +792,8 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -790,22 +808,21 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -818,7 +835,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="39">
+  <fills count="40">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -851,6 +868,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -863,7 +886,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -875,19 +982,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -899,79 +1054,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -983,72 +1066,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="38">
+  <borders count="39">
     <border>
       <left/>
       <right/>
@@ -1277,47 +1300,23 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
         <color auto="1"/>
       </bottom>
       <diagonal/>
@@ -1332,6 +1331,47 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="medium">
         <color auto="1"/>
       </left>
@@ -1420,10 +1460,10 @@
       <right style="medium">
         <color auto="1"/>
       </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1440,20 +1480,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1464,6 +1501,45 @@
         <color theme="4"/>
       </top>
       <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -1484,51 +1560,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -1537,12 +1568,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1560,134 +1600,134 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="16" borderId="35" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="30" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="36" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="34" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="35" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="33" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="35" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="37" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="29" borderId="36" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="9" borderId="36" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="38" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="32" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="30" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="37" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="10" borderId="33" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="11" borderId="34" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="11" borderId="33" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="31" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="32" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="138">
+  <cellXfs count="144">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1719,16 +1759,16 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1737,16 +1777,19 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1755,16 +1798,16 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1773,85 +1816,88 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1860,190 +1906,197 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="1" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="14" fillId="0" borderId="8" xfId="7" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="12" fillId="0" borderId="8" xfId="7" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="14" fillId="0" borderId="11" xfId="7" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="12" fillId="0" borderId="11" xfId="7" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="14" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="5" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="6" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="4" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="16" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="6" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="4" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="14" fillId="0" borderId="14" xfId="7" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="11" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="5" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="14" fillId="0" borderId="16" xfId="7" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="14" fillId="4" borderId="8" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="4" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="12" fillId="0" borderId="14" xfId="7" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="6" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="11" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="6" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="12" fillId="0" borderId="16" xfId="7" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="12" fillId="4" borderId="8" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="4" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="4" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="14" fillId="4" borderId="11" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="12" fillId="4" borderId="11" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="4" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="15" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="14" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="20" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="5" fillId="4" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="4" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="14" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="4" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="14" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="14" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="4" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="8" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="5" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="11" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="10" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="10" fillId="6" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="6" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="4" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="8" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="6" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="4" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="14" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="4" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="8" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="6" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="11" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="9" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="4" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="9" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="4" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="4" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="180" fontId="4" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="4" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2052,183 +2105,188 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="180" fontId="4" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="4" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="180" fontId="4" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="4" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="4" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="4" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="21" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="21" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="4" fillId="6" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="21" fillId="6" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="4" fillId="6" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="4" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="4" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="4" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="4" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="4" fillId="6" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="19" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="19" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="4" fillId="7" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="19" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="4" fillId="7" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="14" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="16" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="11" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="11" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="14" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="14" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2550,7 +2608,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AH43"/>
+  <dimension ref="A1:AH45"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6.14285714285714" style="2" customWidth="1"/>
@@ -2558,7 +2616,7 @@
     <col min="3" max="3" width="47.5714285714286" style="1" customWidth="1"/>
     <col min="4" max="4" width="33.1428571428571" style="1" customWidth="1"/>
     <col min="5" max="5" width="21" style="1" customWidth="1"/>
-    <col min="6" max="6" width="29" style="1" customWidth="1"/>
+    <col min="6" max="6" width="36.2857142857143" style="1" customWidth="1"/>
     <col min="7" max="7" width="19.1428571428571" style="1" customWidth="1"/>
     <col min="8" max="8" width="14.4285714285714" style="2" customWidth="1"/>
     <col min="9" max="9" width="21.5714285714286" style="1" customWidth="1"/>
@@ -2595,22 +2653,22 @@
       <c r="P1" s="4"/>
       <c r="Q1" s="4"/>
       <c r="R1" s="4"/>
-      <c r="S1" s="120"/>
-      <c r="T1" s="120"/>
-      <c r="U1" s="120"/>
-      <c r="V1" s="120"/>
-      <c r="W1" s="120"/>
-      <c r="X1" s="120"/>
-      <c r="Y1" s="120"/>
-      <c r="Z1" s="120"/>
-      <c r="AA1" s="120"/>
-      <c r="AB1" s="120"/>
-      <c r="AC1" s="120"/>
-      <c r="AD1" s="120"/>
-      <c r="AE1" s="120"/>
-      <c r="AF1" s="120"/>
-      <c r="AG1" s="120"/>
-      <c r="AH1" s="137"/>
+      <c r="S1" s="125"/>
+      <c r="T1" s="125"/>
+      <c r="U1" s="125"/>
+      <c r="V1" s="125"/>
+      <c r="W1" s="125"/>
+      <c r="X1" s="125"/>
+      <c r="Y1" s="125"/>
+      <c r="Z1" s="125"/>
+      <c r="AA1" s="125"/>
+      <c r="AB1" s="125"/>
+      <c r="AC1" s="125"/>
+      <c r="AD1" s="125"/>
+      <c r="AE1" s="125"/>
+      <c r="AF1" s="125"/>
+      <c r="AG1" s="125"/>
+      <c r="AH1" s="143"/>
     </row>
     <row r="2" s="1" customFormat="1" ht="32.25" spans="1:18">
       <c r="A2" s="5" t="s">
@@ -2652,19 +2710,19 @@
       <c r="M2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="N2" s="67" t="s">
+      <c r="N2" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="O2" s="68" t="s">
+      <c r="O2" s="70" t="s">
         <v>15</v>
       </c>
-      <c r="P2" s="69" t="s">
+      <c r="P2" s="7" t="s">
         <v>16</v>
       </c>
       <c r="Q2" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="R2" s="121" t="s">
+      <c r="R2" s="126" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2675,28 +2733,28 @@
       <c r="B3" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="138" t="s">
+      <c r="C3" s="144" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="139" t="s">
+      <c r="D3" s="145" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="140" t="s">
+      <c r="E3" s="146" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="140" t="s">
+      <c r="F3" s="146" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="141" t="s">
+      <c r="G3" s="147" t="s">
         <v>24</v>
       </c>
       <c r="H3" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="142" t="s">
+      <c r="I3" s="148" t="s">
         <v>26</v>
       </c>
-      <c r="J3" s="140" t="s">
+      <c r="J3" s="146" t="s">
         <v>27</v>
       </c>
       <c r="K3" s="12">
@@ -2706,103 +2764,103 @@
         <v>4</v>
       </c>
       <c r="M3" s="12">
-        <f t="shared" ref="M3:M16" si="0">L3*400</f>
+        <f t="shared" ref="M3:M18" si="0">L3*400</f>
         <v>1600</v>
       </c>
-      <c r="N3" s="70" t="s">
+      <c r="N3" s="71" t="s">
         <v>28</v>
       </c>
-      <c r="O3" s="71">
+      <c r="O3" s="72">
         <v>0.0682</v>
       </c>
-      <c r="P3" s="72">
-        <f>O3*K3</f>
+      <c r="P3" s="73">
+        <f t="shared" ref="P3:P16" si="1">O3*K3</f>
         <v>110.484</v>
       </c>
       <c r="Q3" s="12"/>
-      <c r="R3" s="122"/>
-      <c r="S3" s="123"/>
+      <c r="R3" s="127"/>
+      <c r="S3" s="128"/>
     </row>
-    <row r="4" s="1" customFormat="1" ht="15.75" spans="1:19">
+    <row r="4" s="1" customFormat="1" ht="51.75" spans="1:19">
       <c r="A4" s="8">
         <v>2</v>
       </c>
       <c r="B4" s="15"/>
-      <c r="C4" s="143" t="s">
+      <c r="C4" s="149" t="s">
         <v>29</v>
       </c>
-      <c r="D4" s="144" t="s">
+      <c r="D4" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="E4" s="145" t="s">
+      <c r="E4" s="150" t="s">
         <v>31</v>
       </c>
-      <c r="F4" s="145" t="s">
+      <c r="F4" s="150" t="s">
         <v>32</v>
       </c>
-      <c r="G4" s="146" t="s">
+      <c r="G4" s="151" t="s">
         <v>33</v>
       </c>
       <c r="H4" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="I4" s="147" t="s">
+      <c r="I4" s="152" t="s">
         <v>26</v>
       </c>
-      <c r="J4" s="145" t="s">
+      <c r="J4" s="150" t="s">
         <v>35</v>
       </c>
       <c r="K4" s="18">
         <v>8850</v>
       </c>
       <c r="L4" s="18">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="M4" s="18">
         <f t="shared" si="0"/>
-        <v>8800</v>
-      </c>
-      <c r="N4" s="73" t="s">
+        <v>9600</v>
+      </c>
+      <c r="N4" s="74" t="s">
         <v>28</v>
       </c>
-      <c r="O4" s="74">
+      <c r="O4" s="75">
         <v>0.0047</v>
       </c>
-      <c r="P4" s="75">
-        <f t="shared" ref="P4:P26" si="1">O4*K4</f>
+      <c r="P4" s="76">
+        <f t="shared" si="1"/>
         <v>41.595</v>
       </c>
       <c r="Q4" s="18"/>
-      <c r="R4" s="124"/>
-      <c r="S4" s="123"/>
+      <c r="R4" s="129"/>
+      <c r="S4" s="128"/>
     </row>
     <row r="5" s="1" customFormat="1" ht="15.75" spans="1:19">
       <c r="A5" s="8">
         <v>3</v>
       </c>
       <c r="B5" s="15"/>
-      <c r="C5" s="143" t="s">
+      <c r="C5" s="149" t="s">
         <v>36</v>
       </c>
-      <c r="D5" s="144" t="s">
+      <c r="D5" s="153" t="s">
         <v>37</v>
       </c>
-      <c r="E5" s="145" t="s">
+      <c r="E5" s="150" t="s">
         <v>22</v>
       </c>
-      <c r="F5" s="145" t="s">
+      <c r="F5" s="150" t="s">
         <v>38</v>
       </c>
-      <c r="G5" s="146" t="s">
+      <c r="G5" s="151" t="s">
         <v>24</v>
       </c>
       <c r="H5" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="I5" s="148" t="s">
+      <c r="I5" s="154" t="s">
         <v>40</v>
       </c>
-      <c r="J5" s="145" t="s">
+      <c r="J5" s="150" t="s">
         <v>41</v>
       </c>
       <c r="K5" s="18">
@@ -2815,47 +2873,47 @@
         <f t="shared" si="0"/>
         <v>400</v>
       </c>
-      <c r="N5" s="73" t="s">
+      <c r="N5" s="74" t="s">
         <v>28</v>
       </c>
-      <c r="O5" s="74">
+      <c r="O5" s="75">
         <v>0.087</v>
       </c>
-      <c r="P5" s="75">
+      <c r="P5" s="76">
         <f t="shared" si="1"/>
         <v>36.54</v>
       </c>
       <c r="Q5" s="18"/>
-      <c r="R5" s="124"/>
-      <c r="S5" s="123"/>
+      <c r="R5" s="129"/>
+      <c r="S5" s="128"/>
     </row>
     <row r="6" s="1" customFormat="1" ht="15.75" spans="1:19">
       <c r="A6" s="8">
         <v>4</v>
       </c>
       <c r="B6" s="15"/>
-      <c r="C6" s="143" t="s">
+      <c r="C6" s="149" t="s">
         <v>42</v>
       </c>
-      <c r="D6" s="144" t="s">
+      <c r="D6" s="153" t="s">
         <v>43</v>
       </c>
-      <c r="E6" s="145" t="s">
+      <c r="E6" s="150" t="s">
         <v>31</v>
       </c>
-      <c r="F6" s="145" t="s">
+      <c r="F6" s="150" t="s">
         <v>44</v>
       </c>
-      <c r="G6" s="146" t="s">
+      <c r="G6" s="151" t="s">
         <v>45</v>
       </c>
       <c r="H6" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="I6" s="148" t="s">
+      <c r="I6" s="154" t="s">
         <v>47</v>
       </c>
-      <c r="J6" s="145" t="s">
+      <c r="J6" s="150" t="s">
         <v>48</v>
       </c>
       <c r="K6" s="18">
@@ -2868,157 +2926,157 @@
         <f t="shared" si="0"/>
         <v>1200</v>
       </c>
-      <c r="N6" s="149" t="s">
+      <c r="N6" s="155" t="s">
         <v>28</v>
       </c>
-      <c r="O6" s="77">
+      <c r="O6" s="78">
         <v>0.0231</v>
       </c>
-      <c r="P6" s="75">
+      <c r="P6" s="76">
         <f t="shared" si="1"/>
         <v>28.182</v>
       </c>
       <c r="Q6" s="18"/>
-      <c r="R6" s="124"/>
-      <c r="S6" s="123"/>
+      <c r="R6" s="129"/>
+      <c r="S6" s="128"/>
     </row>
     <row r="7" s="1" customFormat="1" ht="15.75" spans="1:19">
       <c r="A7" s="8">
         <v>5</v>
       </c>
-      <c r="B7" s="21"/>
-      <c r="C7" s="150" t="s">
+      <c r="B7" s="22"/>
+      <c r="C7" s="156" t="s">
         <v>49</v>
       </c>
-      <c r="D7" s="151" t="s">
+      <c r="D7" s="157" t="s">
         <v>50</v>
       </c>
-      <c r="E7" s="152" t="s">
+      <c r="E7" s="158" t="s">
         <v>31</v>
       </c>
-      <c r="F7" s="152" t="s">
+      <c r="F7" s="158" t="s">
         <v>51</v>
       </c>
-      <c r="G7" s="153" t="s">
+      <c r="G7" s="159" t="s">
         <v>52</v>
       </c>
-      <c r="H7" s="26" t="s">
+      <c r="H7" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="I7" s="154" t="s">
+      <c r="I7" s="160" t="s">
         <v>54</v>
       </c>
-      <c r="J7" s="152" t="s">
+      <c r="J7" s="158" t="s">
         <v>55</v>
       </c>
-      <c r="K7" s="24">
+      <c r="K7" s="25">
         <v>1650</v>
       </c>
-      <c r="L7" s="24">
+      <c r="L7" s="25">
         <v>4</v>
       </c>
-      <c r="M7" s="24">
+      <c r="M7" s="25">
         <f t="shared" si="0"/>
         <v>1600</v>
       </c>
-      <c r="N7" s="155" t="s">
+      <c r="N7" s="161" t="s">
         <v>28</v>
       </c>
-      <c r="O7" s="79">
+      <c r="O7" s="80">
         <v>0.0024</v>
       </c>
-      <c r="P7" s="80">
+      <c r="P7" s="81">
         <f t="shared" si="1"/>
         <v>3.96</v>
       </c>
-      <c r="Q7" s="125"/>
-      <c r="R7" s="126"/>
-      <c r="S7" s="123"/>
+      <c r="Q7" s="130"/>
+      <c r="R7" s="131"/>
+      <c r="S7" s="128"/>
     </row>
     <row r="8" s="1" customFormat="1" ht="15.75" spans="1:19">
       <c r="A8" s="8">
-        <v>17</v>
-      </c>
-      <c r="B8" s="27" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="28" t="s">
         <v>56</v>
       </c>
-      <c r="C8" s="156" t="s">
+      <c r="C8" s="162" t="s">
         <v>57</v>
       </c>
-      <c r="D8" s="157" t="s">
+      <c r="D8" s="163" t="s">
         <v>58</v>
       </c>
-      <c r="E8" s="158" t="s">
+      <c r="E8" s="164" t="s">
         <v>59</v>
       </c>
-      <c r="F8" s="158" t="s">
+      <c r="F8" s="164" t="s">
         <v>60</v>
       </c>
-      <c r="G8" s="159" t="s">
+      <c r="G8" s="165" t="s">
         <v>61</v>
       </c>
-      <c r="H8" s="32" t="s">
+      <c r="H8" s="33" t="s">
         <v>62</v>
       </c>
-      <c r="I8" s="160" t="s">
+      <c r="I8" s="166" t="s">
         <v>26</v>
       </c>
-      <c r="J8" s="159" t="s">
+      <c r="J8" s="165" t="s">
         <v>63</v>
       </c>
-      <c r="K8" s="31">
-        <v>850</v>
-      </c>
-      <c r="L8" s="30">
-        <v>2</v>
-      </c>
-      <c r="M8" s="30">
+      <c r="K8" s="32">
+        <v>1220</v>
+      </c>
+      <c r="L8" s="31">
+        <v>3</v>
+      </c>
+      <c r="M8" s="31">
         <f t="shared" si="0"/>
-        <v>800</v>
-      </c>
-      <c r="N8" s="161" t="s">
+        <v>1200</v>
+      </c>
+      <c r="N8" s="167" t="s">
         <v>28</v>
       </c>
-      <c r="O8" s="82">
-        <v>0.0484</v>
-      </c>
-      <c r="P8" s="83">
+      <c r="O8" s="83">
+        <v>0.045</v>
+      </c>
+      <c r="P8" s="84">
         <f t="shared" si="1"/>
-        <v>41.14</v>
-      </c>
-      <c r="Q8" s="30"/>
-      <c r="R8" s="127"/>
-      <c r="S8" s="123"/>
+        <v>54.9</v>
+      </c>
+      <c r="Q8" s="31"/>
+      <c r="R8" s="132"/>
+      <c r="S8" s="128"/>
     </row>
     <row r="9" s="1" customFormat="1" ht="15.75" spans="1:19">
       <c r="A9" s="8">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="C9" s="138" t="s">
+      <c r="C9" s="144" t="s">
         <v>65</v>
       </c>
-      <c r="D9" s="139" t="s">
+      <c r="D9" s="145" t="s">
         <v>66</v>
       </c>
-      <c r="E9" s="140" t="s">
+      <c r="E9" s="146" t="s">
         <v>67</v>
       </c>
-      <c r="F9" s="140" t="s">
+      <c r="F9" s="146" t="s">
         <v>68</v>
       </c>
-      <c r="G9" s="141" t="s">
+      <c r="G9" s="147" t="s">
         <v>69</v>
       </c>
       <c r="H9" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="I9" s="162" t="s">
+      <c r="I9" s="168" t="s">
         <v>26</v>
       </c>
-      <c r="J9" s="141" t="s">
+      <c r="J9" s="147" t="s">
         <v>63</v>
       </c>
       <c r="K9" s="13">
@@ -3031,105 +3089,105 @@
         <f t="shared" si="0"/>
         <v>2000</v>
       </c>
-      <c r="N9" s="70" t="s">
+      <c r="N9" s="71" t="s">
         <v>28</v>
       </c>
-      <c r="O9" s="71">
+      <c r="O9" s="72">
         <v>0.0052</v>
       </c>
-      <c r="P9" s="72">
+      <c r="P9" s="73">
         <f t="shared" si="1"/>
         <v>10.92</v>
       </c>
       <c r="Q9" s="12"/>
-      <c r="R9" s="122"/>
-      <c r="S9" s="123"/>
+      <c r="R9" s="127"/>
+      <c r="S9" s="128"/>
     </row>
     <row r="10" s="1" customFormat="1" ht="15.75" spans="1:19">
       <c r="A10" s="8">
-        <v>19</v>
-      </c>
-      <c r="B10" s="21"/>
-      <c r="C10" s="150" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="22"/>
+      <c r="C10" s="156" t="s">
         <v>71</v>
       </c>
-      <c r="D10" s="151" t="s">
+      <c r="D10" s="157" t="s">
         <v>72</v>
       </c>
-      <c r="E10" s="152" t="s">
+      <c r="E10" s="158" t="s">
         <v>73</v>
       </c>
-      <c r="F10" s="152" t="s">
+      <c r="F10" s="158" t="s">
         <v>74</v>
       </c>
-      <c r="G10" s="153" t="s">
+      <c r="G10" s="159" t="s">
         <v>75</v>
       </c>
-      <c r="H10" s="26" t="s">
+      <c r="H10" s="27" t="s">
         <v>76</v>
       </c>
-      <c r="I10" s="154" t="s">
+      <c r="I10" s="160" t="s">
         <v>26</v>
       </c>
-      <c r="J10" s="153" t="s">
+      <c r="J10" s="159" t="s">
         <v>63</v>
       </c>
-      <c r="K10" s="25">
+      <c r="K10" s="26">
         <v>420</v>
       </c>
-      <c r="L10" s="24">
+      <c r="L10" s="25">
         <v>1</v>
       </c>
-      <c r="M10" s="24">
+      <c r="M10" s="25">
         <f t="shared" si="0"/>
         <v>400</v>
       </c>
-      <c r="N10" s="84" t="s">
+      <c r="N10" s="85" t="s">
         <v>28</v>
       </c>
-      <c r="O10" s="85">
+      <c r="O10" s="86">
         <v>0.0379</v>
       </c>
-      <c r="P10" s="80">
+      <c r="P10" s="81">
         <f t="shared" si="1"/>
         <v>15.918</v>
       </c>
-      <c r="Q10" s="24"/>
-      <c r="R10" s="126"/>
-      <c r="S10" s="123"/>
+      <c r="Q10" s="25"/>
+      <c r="R10" s="131"/>
+      <c r="S10" s="128"/>
     </row>
-    <row r="11" s="1" customFormat="1" ht="15.75" spans="1:19">
+    <row r="11" s="1" customFormat="1" ht="26.25" spans="1:19">
       <c r="A11" s="8">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="B11" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="C11" s="138" t="s">
+      <c r="C11" s="144" t="s">
         <v>78</v>
       </c>
-      <c r="D11" s="139" t="s">
+      <c r="D11" s="34" t="s">
         <v>79</v>
       </c>
-      <c r="E11" s="140" t="s">
+      <c r="E11" s="146" t="s">
         <v>80</v>
       </c>
-      <c r="F11" s="140" t="s">
+      <c r="F11" s="146" t="s">
         <v>81</v>
       </c>
-      <c r="G11" s="141" t="s">
+      <c r="G11" s="147" t="s">
         <v>33</v>
       </c>
       <c r="H11" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="I11" s="162" t="s">
+      <c r="I11" s="168" t="s">
         <v>26</v>
       </c>
-      <c r="J11" s="140" t="s">
+      <c r="J11" s="146" t="s">
         <v>83</v>
       </c>
-      <c r="K11" s="39">
+      <c r="K11" s="44">
         <v>4900</v>
       </c>
       <c r="L11" s="12">
@@ -3139,50 +3197,50 @@
         <f t="shared" si="0"/>
         <v>4800</v>
       </c>
-      <c r="N11" s="163" t="s">
+      <c r="N11" s="169" t="s">
         <v>28</v>
       </c>
-      <c r="O11" s="71">
+      <c r="O11" s="72">
         <v>0.0011</v>
       </c>
-      <c r="P11" s="72">
+      <c r="P11" s="73">
         <f t="shared" si="1"/>
         <v>5.39</v>
       </c>
       <c r="Q11" s="12"/>
-      <c r="R11" s="122"/>
-      <c r="S11" s="123"/>
+      <c r="R11" s="127"/>
+      <c r="S11" s="128"/>
     </row>
     <row r="12" s="1" customFormat="1" ht="15.75" spans="1:19">
       <c r="A12" s="8">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="B12" s="15"/>
-      <c r="C12" s="143" t="s">
+      <c r="C12" s="149" t="s">
         <v>84</v>
       </c>
-      <c r="D12" s="144" t="s">
+      <c r="D12" s="153" t="s">
         <v>85</v>
       </c>
-      <c r="E12" s="145" t="s">
+      <c r="E12" s="150" t="s">
         <v>80</v>
       </c>
-      <c r="F12" s="145" t="s">
+      <c r="F12" s="150" t="s">
         <v>86</v>
       </c>
-      <c r="G12" s="146" t="s">
+      <c r="G12" s="151" t="s">
         <v>33</v>
       </c>
       <c r="H12" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="I12" s="148" t="s">
+      <c r="I12" s="154" t="s">
         <v>26</v>
       </c>
-      <c r="J12" s="145" t="s">
+      <c r="J12" s="150" t="s">
         <v>88</v>
       </c>
-      <c r="K12" s="43">
+      <c r="K12" s="47">
         <v>1300</v>
       </c>
       <c r="L12" s="18">
@@ -3192,50 +3250,50 @@
         <f t="shared" si="0"/>
         <v>1200</v>
       </c>
-      <c r="N12" s="149" t="s">
+      <c r="N12" s="155" t="s">
         <v>28</v>
       </c>
-      <c r="O12" s="74">
+      <c r="O12" s="75">
         <v>0.0011</v>
       </c>
-      <c r="P12" s="75">
+      <c r="P12" s="76">
         <f t="shared" si="1"/>
         <v>1.43</v>
       </c>
       <c r="Q12" s="18"/>
-      <c r="R12" s="124"/>
-      <c r="S12" s="123"/>
+      <c r="R12" s="129"/>
+      <c r="S12" s="128"/>
     </row>
     <row r="13" s="1" customFormat="1" ht="15.75" spans="1:19">
       <c r="A13" s="8">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="B13" s="15"/>
-      <c r="C13" s="143" t="s">
+      <c r="C13" s="149" t="s">
         <v>89</v>
       </c>
-      <c r="D13" s="144" t="s">
+      <c r="D13" s="153" t="s">
         <v>90</v>
       </c>
-      <c r="E13" s="145" t="s">
+      <c r="E13" s="150" t="s">
         <v>80</v>
       </c>
-      <c r="F13" s="145" t="s">
+      <c r="F13" s="150" t="s">
         <v>91</v>
       </c>
-      <c r="G13" s="146" t="s">
+      <c r="G13" s="151" t="s">
         <v>33</v>
       </c>
       <c r="H13" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="I13" s="148" t="s">
+      <c r="I13" s="154" t="s">
         <v>26</v>
       </c>
-      <c r="J13" s="145" t="s">
+      <c r="J13" s="150" t="s">
         <v>93</v>
       </c>
-      <c r="K13" s="43">
+      <c r="K13" s="47">
         <v>500</v>
       </c>
       <c r="L13" s="18">
@@ -3245,793 +3303,899 @@
         <f t="shared" si="0"/>
         <v>400</v>
       </c>
-      <c r="N13" s="164" t="s">
+      <c r="N13" s="170" t="s">
         <v>28</v>
       </c>
-      <c r="O13" s="88">
+      <c r="O13" s="89">
         <v>0.0012</v>
       </c>
-      <c r="P13" s="75">
+      <c r="P13" s="76">
         <f t="shared" si="1"/>
         <v>0.6</v>
       </c>
-      <c r="Q13" s="43"/>
-      <c r="R13" s="124"/>
-      <c r="S13" s="123"/>
+      <c r="Q13" s="47"/>
+      <c r="R13" s="129"/>
+      <c r="S13" s="128"/>
     </row>
     <row r="14" s="1" customFormat="1" ht="15.75" spans="1:19">
       <c r="A14" s="8">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B14" s="15"/>
-      <c r="C14" s="143" t="s">
+      <c r="C14" s="149" t="s">
         <v>94</v>
       </c>
-      <c r="D14" s="144" t="s">
+      <c r="D14" s="153" t="s">
         <v>95</v>
       </c>
-      <c r="E14" s="145" t="s">
+      <c r="E14" s="150" t="s">
         <v>80</v>
       </c>
-      <c r="F14" s="145" t="s">
+      <c r="F14" s="150" t="s">
         <v>96</v>
       </c>
-      <c r="G14" s="146" t="s">
+      <c r="G14" s="151" t="s">
         <v>33</v>
       </c>
       <c r="H14" s="20" t="s">
         <v>97</v>
       </c>
-      <c r="I14" s="148" t="s">
+      <c r="I14" s="154" t="s">
         <v>26</v>
       </c>
-      <c r="J14" s="145" t="s">
+      <c r="J14" s="150" t="s">
         <v>98</v>
       </c>
-      <c r="K14" s="43">
+      <c r="K14" s="47">
         <v>1300</v>
       </c>
       <c r="L14" s="18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M14" s="18">
         <f t="shared" si="0"/>
-        <v>1200</v>
-      </c>
-      <c r="N14" s="149" t="s">
+        <v>1600</v>
+      </c>
+      <c r="N14" s="155" t="s">
         <v>28</v>
       </c>
-      <c r="O14" s="74">
+      <c r="O14" s="75">
         <v>0.001</v>
       </c>
-      <c r="P14" s="75">
+      <c r="P14" s="76">
         <f t="shared" si="1"/>
         <v>1.3</v>
       </c>
       <c r="Q14" s="18"/>
-      <c r="R14" s="124"/>
-      <c r="S14" s="123"/>
+      <c r="R14" s="129"/>
+      <c r="S14" s="128"/>
     </row>
     <row r="15" s="1" customFormat="1" ht="15.75" spans="1:19">
       <c r="A15" s="8">
-        <v>25</v>
-      </c>
-      <c r="B15" s="21"/>
-      <c r="C15" s="150" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="35"/>
+      <c r="C15" s="36" t="s">
         <v>99</v>
       </c>
-      <c r="D15" s="151" t="s">
+      <c r="D15" s="37" t="s">
         <v>100</v>
       </c>
-      <c r="E15" s="152" t="s">
+      <c r="E15" s="37" t="s">
         <v>80</v>
       </c>
-      <c r="F15" s="152" t="s">
+      <c r="F15" s="37" t="s">
         <v>101</v>
       </c>
-      <c r="G15" s="153" t="s">
+      <c r="G15" s="151" t="s">
+        <v>33</v>
+      </c>
+      <c r="H15" s="38" t="s">
         <v>102</v>
       </c>
-      <c r="H15" s="26" t="s">
+      <c r="I15" s="90"/>
+      <c r="J15" s="91" t="s">
         <v>103</v>
       </c>
-      <c r="I15" s="154" t="s">
-        <v>26</v>
-      </c>
-      <c r="J15" s="152" t="s">
-        <v>104</v>
-      </c>
-      <c r="K15" s="24">
-        <v>420</v>
-      </c>
-      <c r="L15" s="24">
-        <v>1</v>
-      </c>
-      <c r="M15" s="24">
+      <c r="K15" s="92">
+        <v>900</v>
+      </c>
+      <c r="L15" s="37">
+        <v>2</v>
+      </c>
+      <c r="M15" s="18">
         <f t="shared" si="0"/>
-        <v>400</v>
-      </c>
-      <c r="N15" s="155" t="s">
+        <v>800</v>
+      </c>
+      <c r="N15" s="93" t="s">
         <v>28</v>
       </c>
-      <c r="O15" s="85">
-        <v>0.0138</v>
-      </c>
-      <c r="P15" s="80">
+      <c r="O15" s="94">
+        <v>0.0015</v>
+      </c>
+      <c r="P15" s="76">
         <f t="shared" si="1"/>
-        <v>5.796</v>
-      </c>
-      <c r="Q15" s="24"/>
-      <c r="R15" s="126"/>
-      <c r="S15" s="123"/>
+        <v>1.35</v>
+      </c>
+      <c r="Q15" s="133"/>
+      <c r="R15" s="134"/>
+      <c r="S15" s="128"/>
     </row>
     <row r="16" s="1" customFormat="1" ht="15.75" spans="1:19">
       <c r="A16" s="8">
-        <v>30</v>
-      </c>
-      <c r="B16" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="35"/>
+      <c r="C16" s="36" t="s">
+        <v>104</v>
+      </c>
+      <c r="D16" s="37" t="s">
         <v>105</v>
       </c>
-      <c r="C16" s="165" t="s">
+      <c r="E16" s="37" t="s">
+        <v>80</v>
+      </c>
+      <c r="F16" s="37" t="s">
         <v>106</v>
       </c>
-      <c r="D16" s="166" t="s">
+      <c r="G16" s="151" t="s">
+        <v>33</v>
+      </c>
+      <c r="H16" s="38" t="s">
         <v>107</v>
       </c>
-      <c r="E16" s="160" t="s">
+      <c r="I16" s="90"/>
+      <c r="J16" s="91" t="s">
         <v>108</v>
       </c>
-      <c r="F16" s="160" t="s">
-        <v>109</v>
-      </c>
-      <c r="G16" s="167" t="s">
-        <v>110</v>
-      </c>
-      <c r="H16" s="167" t="s">
-        <v>26</v>
-      </c>
-      <c r="I16" s="160" t="s">
-        <v>26</v>
-      </c>
-      <c r="J16" s="35"/>
-      <c r="K16" s="35">
-        <v>420</v>
-      </c>
-      <c r="L16" s="30">
+      <c r="K16" s="92">
+        <v>500</v>
+      </c>
+      <c r="L16" s="37">
         <v>1</v>
       </c>
-      <c r="M16" s="30">
+      <c r="M16" s="18">
         <f t="shared" si="0"/>
         <v>400</v>
       </c>
-      <c r="N16" s="89" t="s">
-        <v>111</v>
-      </c>
-      <c r="O16" s="82">
-        <v>0.49325</v>
-      </c>
-      <c r="P16" s="83">
+      <c r="N16" s="93" t="s">
+        <v>28</v>
+      </c>
+      <c r="O16" s="94">
+        <v>0.0012</v>
+      </c>
+      <c r="P16" s="76">
         <f t="shared" si="1"/>
-        <v>207.165</v>
-      </c>
-      <c r="Q16" s="30"/>
-      <c r="R16" s="127">
-        <v>0.441</v>
-      </c>
-      <c r="S16" s="123"/>
+        <v>0.6</v>
+      </c>
+      <c r="Q16" s="133"/>
+      <c r="R16" s="134"/>
+      <c r="S16" s="128"/>
     </row>
     <row r="17" s="1" customFormat="1" ht="15.75" spans="1:19">
       <c r="A17" s="8">
-        <v>31</v>
-      </c>
-      <c r="B17" s="36" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="22"/>
+      <c r="C17" s="156" t="s">
+        <v>109</v>
+      </c>
+      <c r="D17" s="157" t="s">
+        <v>110</v>
+      </c>
+      <c r="E17" s="158" t="s">
+        <v>80</v>
+      </c>
+      <c r="F17" s="158" t="s">
+        <v>111</v>
+      </c>
+      <c r="G17" s="159" t="s">
         <v>112</v>
       </c>
-      <c r="C17" s="168" t="s">
+      <c r="H17" s="27" t="s">
         <v>113</v>
       </c>
-      <c r="D17" s="169" t="s">
+      <c r="I17" s="160" t="s">
+        <v>26</v>
+      </c>
+      <c r="J17" s="158" t="s">
         <v>114</v>
       </c>
-      <c r="E17" s="39"/>
-      <c r="F17" s="162" t="s">
-        <v>115</v>
-      </c>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="14"/>
-      <c r="J17" s="14"/>
-      <c r="K17" s="14"/>
-      <c r="L17" s="12">
+      <c r="K17" s="25">
+        <v>420</v>
+      </c>
+      <c r="L17" s="25">
         <v>1</v>
       </c>
-      <c r="M17" s="90">
-        <f>L17*900</f>
-        <v>900</v>
-      </c>
-      <c r="N17" s="91" t="s">
-        <v>116</v>
-      </c>
-      <c r="O17" s="92">
-        <v>21.26</v>
-      </c>
-      <c r="P17" s="93">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q17" s="39"/>
-      <c r="R17" s="122">
-        <v>21.26</v>
-      </c>
-      <c r="S17" s="123"/>
+      <c r="M17" s="25">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="N17" s="161" t="s">
+        <v>28</v>
+      </c>
+      <c r="O17" s="86">
+        <v>0.0138</v>
+      </c>
+      <c r="P17" s="81">
+        <f t="shared" ref="P17:P28" si="2">O17*K17</f>
+        <v>5.796</v>
+      </c>
+      <c r="Q17" s="25"/>
+      <c r="R17" s="131"/>
+      <c r="S17" s="128"/>
     </row>
     <row r="18" s="1" customFormat="1" ht="15.75" spans="1:19">
       <c r="A18" s="8">
-        <v>32</v>
-      </c>
-      <c r="B18" s="40"/>
-      <c r="C18" s="170" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="28" t="s">
+        <v>115</v>
+      </c>
+      <c r="C18" s="171" t="s">
+        <v>116</v>
+      </c>
+      <c r="D18" s="172" t="s">
         <v>117</v>
       </c>
-      <c r="D18" s="171" t="s">
+      <c r="E18" s="166" t="s">
         <v>118</v>
       </c>
-      <c r="E18" s="148" t="s">
+      <c r="F18" s="166" t="s">
         <v>119</v>
       </c>
-      <c r="F18" s="148" t="s">
+      <c r="G18" s="173" t="s">
         <v>120</v>
       </c>
-      <c r="G18" s="147" t="s">
+      <c r="H18" s="173" t="s">
+        <v>26</v>
+      </c>
+      <c r="I18" s="166" t="s">
+        <v>26</v>
+      </c>
+      <c r="J18" s="41"/>
+      <c r="K18" s="41">
+        <v>420</v>
+      </c>
+      <c r="L18" s="31">
+        <v>1</v>
+      </c>
+      <c r="M18" s="31">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="N18" s="95" t="s">
         <v>121</v>
       </c>
-      <c r="H18" s="20" t="s">
-        <v>122</v>
-      </c>
-      <c r="I18" s="148" t="s">
-        <v>26</v>
-      </c>
-      <c r="J18" s="147" t="s">
-        <v>63</v>
-      </c>
-      <c r="K18" s="20">
-        <v>420</v>
-      </c>
-      <c r="L18" s="18">
-        <v>1</v>
-      </c>
-      <c r="M18" s="18">
-        <f t="shared" ref="M18:M26" si="2">L18*400</f>
-        <v>400</v>
-      </c>
-      <c r="N18" s="94" t="s">
-        <v>28</v>
-      </c>
-      <c r="O18" s="88">
-        <v>0.2868</v>
-      </c>
-      <c r="P18" s="95">
-        <f t="shared" si="1"/>
-        <v>120.456</v>
-      </c>
-      <c r="Q18" s="43"/>
-      <c r="R18" s="124"/>
-      <c r="S18" s="123"/>
+      <c r="O18" s="83">
+        <v>0.49325</v>
+      </c>
+      <c r="P18" s="84">
+        <f t="shared" si="2"/>
+        <v>207.165</v>
+      </c>
+      <c r="Q18" s="31"/>
+      <c r="R18" s="132">
+        <v>0.441</v>
+      </c>
+      <c r="S18" s="128"/>
     </row>
     <row r="19" s="1" customFormat="1" ht="15.75" spans="1:19">
       <c r="A19" s="8">
-        <v>34</v>
-      </c>
-      <c r="B19" s="40"/>
-      <c r="C19" s="170" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="C19" s="174" t="s">
         <v>123</v>
       </c>
-      <c r="D19" s="171" t="s">
+      <c r="D19" s="175" t="s">
         <v>124</v>
       </c>
-      <c r="E19" s="148" t="s">
-        <v>119</v>
-      </c>
-      <c r="F19" s="148" t="s">
+      <c r="E19" s="44"/>
+      <c r="F19" s="168" t="s">
         <v>125</v>
       </c>
-      <c r="G19" s="147" t="s">
+      <c r="G19" s="14"/>
+      <c r="H19" s="14"/>
+      <c r="I19" s="14"/>
+      <c r="J19" s="14"/>
+      <c r="K19" s="14">
+        <v>920</v>
+      </c>
+      <c r="L19" s="12">
+        <v>1</v>
+      </c>
+      <c r="M19" s="96">
+        <f>L19*900</f>
+        <v>900</v>
+      </c>
+      <c r="N19" s="97" t="s">
         <v>126</v>
       </c>
-      <c r="H19" s="147" t="s">
-        <v>26</v>
-      </c>
-      <c r="I19" s="148" t="s">
-        <v>26</v>
-      </c>
-      <c r="J19" s="147" t="s">
-        <v>63</v>
-      </c>
-      <c r="K19" s="20">
-        <v>420</v>
-      </c>
-      <c r="L19" s="18">
-        <v>1</v>
-      </c>
-      <c r="M19" s="18">
+      <c r="O19" s="98">
+        <v>21.26</v>
+      </c>
+      <c r="P19" s="99">
         <f t="shared" si="2"/>
-        <v>400</v>
-      </c>
-      <c r="N19" s="164" t="s">
-        <v>127</v>
-      </c>
-      <c r="O19" s="96">
-        <v>5</v>
-      </c>
-      <c r="P19" s="95">
-        <f t="shared" si="1"/>
-        <v>2100</v>
-      </c>
-      <c r="Q19" s="128"/>
-      <c r="R19" s="124">
-        <v>2.756</v>
-      </c>
-      <c r="S19" s="123"/>
+        <v>19559.2</v>
+      </c>
+      <c r="Q19" s="44"/>
+      <c r="R19" s="127">
+        <v>21.26</v>
+      </c>
+      <c r="S19" s="128"/>
     </row>
     <row r="20" s="1" customFormat="1" ht="15.75" spans="1:19">
       <c r="A20" s="8">
-        <v>35</v>
-      </c>
-      <c r="B20" s="44"/>
-      <c r="C20" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" s="15"/>
+      <c r="C20" s="176" t="s">
+        <v>127</v>
+      </c>
+      <c r="D20" s="177" t="s">
         <v>128</v>
       </c>
-      <c r="D20" s="154" t="s">
+      <c r="E20" s="154" t="s">
         <v>129</v>
       </c>
-      <c r="E20" s="154" t="s">
+      <c r="F20" s="154" t="s">
         <v>130</v>
       </c>
-      <c r="F20" s="47" t="s">
+      <c r="G20" s="152" t="s">
         <v>131</v>
       </c>
-      <c r="G20" s="154" t="s">
+      <c r="H20" s="20" t="s">
         <v>132</v>
-      </c>
-      <c r="H20" s="48" t="s">
-        <v>133</v>
       </c>
       <c r="I20" s="154" t="s">
         <v>26</v>
       </c>
-      <c r="J20" s="172" t="s">
+      <c r="J20" s="152" t="s">
         <v>63</v>
       </c>
-      <c r="K20" s="26">
+      <c r="K20" s="20">
         <v>420</v>
       </c>
-      <c r="L20" s="24">
+      <c r="L20" s="18">
         <v>1</v>
       </c>
-      <c r="M20" s="24">
+      <c r="M20" s="18">
+        <f t="shared" ref="M20:M28" si="3">L20*400</f>
+        <v>400</v>
+      </c>
+      <c r="N20" s="100" t="s">
+        <v>28</v>
+      </c>
+      <c r="O20" s="89">
+        <v>0.2868</v>
+      </c>
+      <c r="P20" s="101">
         <f t="shared" si="2"/>
-        <v>400</v>
-      </c>
-      <c r="N20" s="97" t="s">
-        <v>28</v>
-      </c>
-      <c r="O20" s="79">
-        <v>0.3607</v>
-      </c>
-      <c r="P20" s="95">
-        <f>O20*K20</f>
-        <v>151.494</v>
-      </c>
-      <c r="Q20" s="46"/>
-      <c r="R20" s="126"/>
-      <c r="S20" s="123"/>
+        <v>120.456</v>
+      </c>
+      <c r="Q20" s="47"/>
+      <c r="R20" s="129"/>
+      <c r="S20" s="128"/>
     </row>
     <row r="21" s="1" customFormat="1" ht="15.75" spans="1:19">
       <c r="A21" s="8">
-        <v>38</v>
-      </c>
-      <c r="B21" s="49" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="15"/>
+      <c r="C21" s="176" t="s">
+        <v>133</v>
+      </c>
+      <c r="D21" s="177" t="s">
         <v>134</v>
       </c>
-      <c r="C21" s="173" t="s">
+      <c r="E21" s="154" t="s">
+        <v>129</v>
+      </c>
+      <c r="F21" s="154" t="s">
         <v>135</v>
       </c>
-      <c r="D21" s="174" t="s">
+      <c r="G21" s="152" t="s">
         <v>136</v>
       </c>
-      <c r="E21" s="175" t="s">
-        <v>108</v>
-      </c>
-      <c r="F21" s="175" t="s">
+      <c r="H21" s="152" t="s">
+        <v>26</v>
+      </c>
+      <c r="I21" s="154" t="s">
+        <v>26</v>
+      </c>
+      <c r="J21" s="152" t="s">
+        <v>63</v>
+      </c>
+      <c r="K21" s="20">
+        <v>420</v>
+      </c>
+      <c r="L21" s="18">
+        <v>1</v>
+      </c>
+      <c r="M21" s="18">
+        <f t="shared" si="3"/>
+        <v>400</v>
+      </c>
+      <c r="N21" s="170" t="s">
         <v>137</v>
       </c>
-      <c r="G21" s="52"/>
-      <c r="H21" s="53"/>
-      <c r="I21" s="98"/>
-      <c r="J21" s="98"/>
-      <c r="K21" s="98"/>
-      <c r="L21" s="99">
-        <v>1</v>
-      </c>
-      <c r="M21" s="99">
+      <c r="O21" s="102">
+        <v>5</v>
+      </c>
+      <c r="P21" s="101">
         <f t="shared" si="2"/>
-        <v>400</v>
-      </c>
-      <c r="N21" s="100"/>
-      <c r="O21" s="101"/>
-      <c r="P21" s="102">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q21" s="129"/>
-      <c r="R21" s="130" t="s">
-        <v>138</v>
-      </c>
-      <c r="S21" s="123"/>
+        <v>2100</v>
+      </c>
+      <c r="Q21" s="135"/>
+      <c r="R21" s="129">
+        <v>2.756</v>
+      </c>
+      <c r="S21" s="128"/>
     </row>
     <row r="22" s="1" customFormat="1" ht="15.75" spans="1:19">
       <c r="A22" s="8">
-        <v>39</v>
-      </c>
-      <c r="B22" s="21"/>
-      <c r="C22" s="176" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" s="22"/>
+      <c r="C22" s="48" t="s">
+        <v>138</v>
+      </c>
+      <c r="D22" s="160" t="s">
         <v>139</v>
       </c>
-      <c r="D22" s="177" t="s">
+      <c r="E22" s="160" t="s">
         <v>140</v>
       </c>
-      <c r="E22" s="154" t="s">
-        <v>108</v>
-      </c>
-      <c r="F22" s="154" t="s">
+      <c r="F22" s="50" t="s">
         <v>141</v>
       </c>
-      <c r="G22" s="46"/>
-      <c r="H22" s="26"/>
-      <c r="I22" s="26"/>
-      <c r="J22" s="26"/>
-      <c r="K22" s="26"/>
-      <c r="L22" s="24">
+      <c r="G22" s="160" t="s">
+        <v>142</v>
+      </c>
+      <c r="H22" s="51" t="s">
+        <v>143</v>
+      </c>
+      <c r="I22" s="160" t="s">
+        <v>26</v>
+      </c>
+      <c r="J22" s="178" t="s">
+        <v>63</v>
+      </c>
+      <c r="K22" s="27">
+        <v>420</v>
+      </c>
+      <c r="L22" s="25">
         <v>1</v>
       </c>
-      <c r="M22" s="24">
+      <c r="M22" s="25">
+        <f t="shared" si="3"/>
+        <v>400</v>
+      </c>
+      <c r="N22" s="103" t="s">
+        <v>28</v>
+      </c>
+      <c r="O22" s="80">
+        <v>0.3607</v>
+      </c>
+      <c r="P22" s="104">
         <f t="shared" si="2"/>
-        <v>400</v>
-      </c>
-      <c r="N22" s="178" t="s">
-        <v>142</v>
-      </c>
-      <c r="O22" s="104">
-        <v>0.8662</v>
-      </c>
-      <c r="P22" s="105">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q22" s="131"/>
-      <c r="R22" s="126">
-        <v>0.8662</v>
-      </c>
-      <c r="S22" s="123"/>
+        <v>151.494</v>
+      </c>
+      <c r="Q22" s="49"/>
+      <c r="R22" s="131"/>
+      <c r="S22" s="128"/>
     </row>
     <row r="23" s="1" customFormat="1" ht="15.75" spans="1:19">
       <c r="A23" s="8">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="C23" s="138" t="s">
         <v>144</v>
       </c>
-      <c r="D23" s="139" t="s">
+      <c r="C23" s="179" t="s">
         <v>145</v>
       </c>
-      <c r="E23" s="140" t="s">
+      <c r="D23" s="180" t="s">
         <v>146</v>
       </c>
-      <c r="F23" s="140" t="s">
+      <c r="E23" s="181" t="s">
+        <v>118</v>
+      </c>
+      <c r="F23" s="181" t="s">
         <v>147</v>
       </c>
-      <c r="G23" s="140" t="s">
+      <c r="G23" s="54"/>
+      <c r="H23" s="55"/>
+      <c r="I23" s="105"/>
+      <c r="J23" s="105"/>
+      <c r="K23" s="105"/>
+      <c r="L23" s="54">
+        <v>1</v>
+      </c>
+      <c r="M23" s="54">
+        <f t="shared" si="3"/>
+        <v>400</v>
+      </c>
+      <c r="N23" s="106"/>
+      <c r="O23" s="107"/>
+      <c r="P23" s="108">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q23" s="136"/>
+      <c r="R23" s="137" t="s">
         <v>148</v>
       </c>
-      <c r="H23" s="56"/>
-      <c r="I23" s="56"/>
-      <c r="J23" s="12"/>
-      <c r="K23" s="56">
-        <v>800</v>
-      </c>
-      <c r="L23" s="12">
-        <v>2</v>
-      </c>
-      <c r="M23" s="56">
-        <f t="shared" si="2"/>
-        <v>800</v>
-      </c>
-      <c r="N23" s="106" t="s">
-        <v>149</v>
-      </c>
-      <c r="O23" s="107">
-        <v>1.74</v>
-      </c>
-      <c r="P23" s="93">
-        <f t="shared" si="1"/>
-        <v>1392</v>
-      </c>
-      <c r="Q23" s="39"/>
-      <c r="R23" s="122"/>
-      <c r="S23" s="123"/>
+      <c r="S23" s="128"/>
     </row>
     <row r="24" s="1" customFormat="1" ht="15.75" spans="1:19">
       <c r="A24" s="8">
-        <v>42</v>
-      </c>
-      <c r="B24" s="15"/>
-      <c r="C24" s="143" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" s="22"/>
+      <c r="C24" s="182" t="s">
+        <v>149</v>
+      </c>
+      <c r="D24" s="183" t="s">
         <v>150</v>
       </c>
-      <c r="D24" s="144" t="s">
+      <c r="E24" s="160" t="s">
+        <v>118</v>
+      </c>
+      <c r="F24" s="160" t="s">
         <v>151</v>
       </c>
-      <c r="E24" s="145" t="s">
+      <c r="G24" s="49"/>
+      <c r="H24" s="27"/>
+      <c r="I24" s="27"/>
+      <c r="J24" s="27"/>
+      <c r="K24" s="27">
+        <v>420</v>
+      </c>
+      <c r="L24" s="25">
+        <v>1</v>
+      </c>
+      <c r="M24" s="25">
+        <f t="shared" si="3"/>
+        <v>400</v>
+      </c>
+      <c r="N24" s="184" t="s">
         <v>152</v>
       </c>
-      <c r="F24" s="145" t="s">
-        <v>152</v>
-      </c>
-      <c r="G24" s="145" t="s">
-        <v>148</v>
-      </c>
-      <c r="H24" s="57"/>
-      <c r="I24" s="57"/>
-      <c r="J24" s="18"/>
-      <c r="K24" s="57">
-        <v>420</v>
-      </c>
-      <c r="L24" s="18">
-        <v>1</v>
-      </c>
-      <c r="M24" s="57">
+      <c r="O24" s="110">
+        <v>0.8662</v>
+      </c>
+      <c r="P24" s="104">
         <f t="shared" si="2"/>
-        <v>400</v>
-      </c>
-      <c r="N24" s="108" t="s">
-        <v>149</v>
-      </c>
-      <c r="O24" s="88">
-        <v>0.329</v>
-      </c>
-      <c r="P24" s="95">
-        <f t="shared" si="1"/>
-        <v>138.18</v>
-      </c>
-      <c r="Q24" s="43"/>
-      <c r="R24" s="124"/>
-      <c r="S24" s="123"/>
+        <v>363.804</v>
+      </c>
+      <c r="Q24" s="138"/>
+      <c r="R24" s="131">
+        <v>0.8662</v>
+      </c>
+      <c r="S24" s="128"/>
     </row>
     <row r="25" s="1" customFormat="1" ht="15.75" spans="1:19">
       <c r="A25" s="8">
-        <v>43</v>
-      </c>
-      <c r="B25" s="15"/>
-      <c r="C25" s="179" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="D25" s="180" t="s">
+      <c r="C25" s="144" t="s">
         <v>154</v>
       </c>
-      <c r="E25" s="180" t="s">
+      <c r="D25" s="145" t="s">
         <v>155</v>
       </c>
-      <c r="F25" s="59" t="s">
-        <v>155</v>
-      </c>
-      <c r="G25" s="59"/>
-      <c r="H25" s="59"/>
-      <c r="I25" s="59"/>
-      <c r="J25" s="59"/>
-      <c r="K25" s="59"/>
-      <c r="L25" s="109">
-        <v>3</v>
-      </c>
-      <c r="M25" s="109">
+      <c r="E25" s="146" t="s">
+        <v>156</v>
+      </c>
+      <c r="F25" s="146" t="s">
+        <v>157</v>
+      </c>
+      <c r="G25" s="146" t="s">
+        <v>158</v>
+      </c>
+      <c r="H25" s="58"/>
+      <c r="I25" s="58"/>
+      <c r="J25" s="12"/>
+      <c r="K25" s="58">
+        <v>800</v>
+      </c>
+      <c r="L25" s="12">
+        <v>2</v>
+      </c>
+      <c r="M25" s="58">
+        <f t="shared" si="3"/>
+        <v>800</v>
+      </c>
+      <c r="N25" s="111" t="s">
+        <v>159</v>
+      </c>
+      <c r="O25" s="112">
+        <v>1.74</v>
+      </c>
+      <c r="P25" s="99">
         <f t="shared" si="2"/>
-        <v>1200</v>
-      </c>
-      <c r="N25" s="59"/>
-      <c r="O25" s="110"/>
-      <c r="P25" s="111">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q25" s="132" t="s">
-        <v>156</v>
-      </c>
-      <c r="R25" s="133"/>
-      <c r="S25" s="123"/>
+        <v>1392</v>
+      </c>
+      <c r="Q25" s="44"/>
+      <c r="R25" s="127"/>
+      <c r="S25" s="128"/>
     </row>
     <row r="26" s="1" customFormat="1" ht="15.75" spans="1:19">
       <c r="A26" s="8">
-        <v>44</v>
-      </c>
-      <c r="B26" s="21"/>
-      <c r="C26" s="181" t="s">
-        <v>157</v>
-      </c>
-      <c r="D26" s="61" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26" s="15"/>
+      <c r="C26" s="149" t="s">
+        <v>160</v>
+      </c>
+      <c r="D26" s="153" t="s">
+        <v>161</v>
+      </c>
+      <c r="E26" s="150" t="s">
+        <v>162</v>
+      </c>
+      <c r="F26" s="150" t="s">
+        <v>162</v>
+      </c>
+      <c r="G26" s="150" t="s">
         <v>158</v>
       </c>
-      <c r="E26" s="182" t="s">
+      <c r="H26" s="59"/>
+      <c r="I26" s="59"/>
+      <c r="J26" s="18"/>
+      <c r="K26" s="59">
+        <v>420</v>
+      </c>
+      <c r="L26" s="18">
+        <v>1</v>
+      </c>
+      <c r="M26" s="59">
+        <f t="shared" si="3"/>
+        <v>400</v>
+      </c>
+      <c r="N26" s="113" t="s">
         <v>159</v>
       </c>
-      <c r="F26" s="61" t="s">
-        <v>159</v>
-      </c>
-      <c r="G26" s="61"/>
-      <c r="H26" s="61"/>
-      <c r="I26" s="61"/>
-      <c r="J26" s="61"/>
-      <c r="K26" s="61"/>
-      <c r="L26" s="112">
+      <c r="O26" s="89">
+        <v>0.329</v>
+      </c>
+      <c r="P26" s="101">
+        <f t="shared" si="2"/>
+        <v>138.18</v>
+      </c>
+      <c r="Q26" s="47"/>
+      <c r="R26" s="129"/>
+      <c r="S26" s="128"/>
+    </row>
+    <row r="27" s="1" customFormat="1" ht="15.75" spans="1:19">
+      <c r="A27" s="8">
+        <v>25</v>
+      </c>
+      <c r="B27" s="15"/>
+      <c r="C27" s="185" t="s">
+        <v>163</v>
+      </c>
+      <c r="D27" s="186" t="s">
+        <v>164</v>
+      </c>
+      <c r="E27" s="186" t="s">
+        <v>165</v>
+      </c>
+      <c r="F27" s="61" t="s">
+        <v>165</v>
+      </c>
+      <c r="G27" s="61"/>
+      <c r="H27" s="61"/>
+      <c r="I27" s="61"/>
+      <c r="J27" s="61"/>
+      <c r="K27" s="61"/>
+      <c r="L27" s="114">
         <v>5</v>
       </c>
-      <c r="M26" s="112">
-        <f t="shared" si="2"/>
+      <c r="M27" s="114">
+        <f t="shared" si="3"/>
         <v>2000</v>
       </c>
-      <c r="N26" s="61"/>
-      <c r="O26" s="113"/>
-      <c r="P26" s="114">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q26" s="134" t="s">
-        <v>156</v>
-      </c>
-      <c r="R26" s="135"/>
-      <c r="S26" s="123"/>
-    </row>
-    <row r="27" s="1" customFormat="1" spans="3:19">
-      <c r="C27" s="62"/>
-      <c r="D27" s="63"/>
-      <c r="E27" s="62"/>
-      <c r="G27" s="62"/>
-      <c r="H27" s="62"/>
-      <c r="I27" s="62"/>
-      <c r="J27" s="62"/>
-      <c r="K27" s="62"/>
-      <c r="L27" s="115" t="s">
-        <v>160</v>
-      </c>
-      <c r="M27" s="115"/>
-      <c r="N27" s="115"/>
+      <c r="N27" s="61"/>
       <c r="O27" s="115"/>
       <c r="P27" s="116">
-        <f>SUM(P3:P26)</f>
-        <v>4412.55</v>
-      </c>
-      <c r="Q27" s="62"/>
-      <c r="R27" s="62"/>
-      <c r="S27" s="123"/>
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q27" s="139" t="s">
+        <v>166</v>
+      </c>
+      <c r="R27" s="140"/>
+      <c r="S27" s="128"/>
     </row>
-    <row r="28" s="1" customFormat="1" ht="15.75" spans="3:19">
-      <c r="C28" s="62"/>
-      <c r="E28" s="53"/>
-      <c r="F28" s="53"/>
-      <c r="G28" s="62"/>
-      <c r="H28" s="62"/>
-      <c r="I28" s="62"/>
-      <c r="J28" s="62"/>
-      <c r="K28" s="62"/>
-      <c r="L28" s="117" t="s">
-        <v>161</v>
-      </c>
-      <c r="M28" s="118"/>
-      <c r="N28" s="118"/>
+    <row r="28" s="1" customFormat="1" ht="15.75" spans="1:19">
+      <c r="A28" s="8">
+        <v>26</v>
+      </c>
+      <c r="B28" s="22"/>
+      <c r="C28" s="187" t="s">
+        <v>167</v>
+      </c>
+      <c r="D28" s="63" t="s">
+        <v>168</v>
+      </c>
+      <c r="E28" s="188" t="s">
+        <v>169</v>
+      </c>
+      <c r="F28" s="63" t="s">
+        <v>169</v>
+      </c>
+      <c r="G28" s="63"/>
+      <c r="H28" s="63"/>
+      <c r="I28" s="63"/>
+      <c r="J28" s="63"/>
+      <c r="K28" s="63"/>
+      <c r="L28" s="117">
+        <v>3</v>
+      </c>
+      <c r="M28" s="117">
+        <f t="shared" si="3"/>
+        <v>1200</v>
+      </c>
+      <c r="N28" s="63"/>
       <c r="O28" s="118"/>
       <c r="P28" s="119">
-        <f>P27/400</f>
-        <v>11.031375</v>
-      </c>
-      <c r="Q28" s="62"/>
-      <c r="R28" s="62"/>
-      <c r="S28" s="123"/>
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q28" s="141" t="s">
+        <v>166</v>
+      </c>
+      <c r="R28" s="142"/>
+      <c r="S28" s="128"/>
     </row>
-    <row r="29" s="1" customFormat="1" spans="4:19">
-      <c r="D29" s="64"/>
-      <c r="E29" s="53"/>
-      <c r="H29" s="2"/>
-      <c r="R29" s="123"/>
-      <c r="S29" s="123"/>
+    <row r="29" s="1" customFormat="1" spans="3:19">
+      <c r="C29" s="64"/>
+      <c r="D29" s="65"/>
+      <c r="E29" s="64"/>
+      <c r="G29" s="64"/>
+      <c r="H29" s="64"/>
+      <c r="I29" s="64"/>
+      <c r="J29" s="64"/>
+      <c r="K29" s="64"/>
+      <c r="L29" s="120" t="s">
+        <v>170</v>
+      </c>
+      <c r="M29" s="120"/>
+      <c r="N29" s="120"/>
+      <c r="O29" s="120"/>
+      <c r="P29" s="121">
+        <f>SUM(P3:P28)</f>
+        <v>24351.264</v>
+      </c>
+      <c r="Q29" s="64"/>
+      <c r="R29" s="64"/>
+      <c r="S29" s="128"/>
     </row>
-    <row r="30" s="1" customFormat="1" spans="4:19">
-      <c r="D30" s="53"/>
-      <c r="H30" s="2"/>
-      <c r="R30" s="123"/>
-      <c r="S30" s="123"/>
+    <row r="30" s="1" customFormat="1" ht="15.75" spans="3:19">
+      <c r="C30" s="64"/>
+      <c r="E30" s="66"/>
+      <c r="F30" s="66"/>
+      <c r="G30" s="64"/>
+      <c r="H30" s="64"/>
+      <c r="I30" s="64"/>
+      <c r="J30" s="64"/>
+      <c r="K30" s="64"/>
+      <c r="L30" s="122" t="s">
+        <v>171</v>
+      </c>
+      <c r="M30" s="123"/>
+      <c r="N30" s="123"/>
+      <c r="O30" s="123"/>
+      <c r="P30" s="124">
+        <f>P29/400</f>
+        <v>60.87816</v>
+      </c>
+      <c r="Q30" s="64"/>
+      <c r="R30" s="64"/>
+      <c r="S30" s="128"/>
     </row>
-    <row r="31" s="1" customFormat="1" spans="3:19">
-      <c r="C31" s="65"/>
-      <c r="D31" s="53"/>
+    <row r="31" s="1" customFormat="1" spans="4:19">
+      <c r="D31" s="67"/>
+      <c r="E31" s="66"/>
       <c r="H31" s="2"/>
-      <c r="R31" s="123"/>
-      <c r="S31" s="123"/>
+      <c r="R31" s="128"/>
+      <c r="S31" s="128"/>
     </row>
-    <row r="32" s="1" customFormat="1" spans="8:19">
+    <row r="32" s="1" customFormat="1" spans="4:19">
+      <c r="D32" s="66"/>
       <c r="H32" s="2"/>
-      <c r="R32" s="123"/>
-      <c r="S32" s="123"/>
+      <c r="R32" s="128"/>
+      <c r="S32" s="128"/>
     </row>
-    <row r="33" s="1" customFormat="1" spans="8:19">
+    <row r="33" s="1" customFormat="1" spans="3:19">
+      <c r="C33" s="67"/>
+      <c r="D33" s="66"/>
       <c r="H33" s="2"/>
-      <c r="R33" s="123"/>
-      <c r="S33" s="123"/>
+      <c r="R33" s="128"/>
+      <c r="S33" s="128"/>
     </row>
     <row r="34" s="1" customFormat="1" spans="8:19">
       <c r="H34" s="2"/>
-      <c r="R34" s="123"/>
-      <c r="S34" s="123"/>
+      <c r="R34" s="128"/>
+      <c r="S34" s="128"/>
     </row>
     <row r="35" s="1" customFormat="1" spans="8:19">
       <c r="H35" s="2"/>
-      <c r="R35" s="123"/>
-      <c r="S35" s="123"/>
+      <c r="R35" s="128"/>
+      <c r="S35" s="128"/>
     </row>
-    <row r="36" s="1" customFormat="1" ht="15.75" customHeight="1" spans="8:19">
+    <row r="36" s="1" customFormat="1" spans="8:19">
       <c r="H36" s="2"/>
-      <c r="R36" s="123"/>
-      <c r="S36" s="123"/>
+      <c r="R36" s="128"/>
+      <c r="S36" s="128"/>
     </row>
     <row r="37" s="1" customFormat="1" spans="8:19">
       <c r="H37" s="2"/>
-      <c r="R37" s="123"/>
-      <c r="S37" s="123"/>
+      <c r="R37" s="128"/>
+      <c r="S37" s="128"/>
     </row>
-    <row r="38" s="1" customFormat="1" spans="8:19">
+    <row r="38" s="1" customFormat="1" ht="15.75" customHeight="1" spans="8:19">
       <c r="H38" s="2"/>
-      <c r="R38" s="123"/>
-      <c r="S38" s="123"/>
+      <c r="R38" s="128"/>
+      <c r="S38" s="128"/>
     </row>
     <row r="39" s="1" customFormat="1" spans="8:19">
       <c r="H39" s="2"/>
-      <c r="R39" s="123"/>
-      <c r="S39" s="123"/>
+      <c r="R39" s="128"/>
+      <c r="S39" s="128"/>
     </row>
     <row r="40" s="1" customFormat="1" spans="8:19">
       <c r="H40" s="2"/>
-      <c r="R40" s="123"/>
-      <c r="S40" s="123"/>
+      <c r="R40" s="128"/>
+      <c r="S40" s="128"/>
     </row>
     <row r="41" s="1" customFormat="1" spans="8:19">
       <c r="H41" s="2"/>
-      <c r="R41" s="123"/>
-      <c r="S41" s="123"/>
+      <c r="R41" s="128"/>
+      <c r="S41" s="128"/>
     </row>
-    <row r="42" s="1" customFormat="1" spans="1:17">
-      <c r="A42" s="2"/>
-      <c r="H42" s="66"/>
-      <c r="Q42" s="136"/>
+    <row r="42" s="1" customFormat="1" spans="8:19">
+      <c r="H42" s="2"/>
+      <c r="R42" s="128"/>
+      <c r="S42" s="128"/>
     </row>
-    <row r="43" s="1" customFormat="1" spans="1:17">
-      <c r="A43" s="2"/>
-      <c r="H43" s="66"/>
-      <c r="Q43" s="136"/>
+    <row r="43" s="1" customFormat="1" spans="8:19">
+      <c r="H43" s="2"/>
+      <c r="R43" s="128"/>
+      <c r="S43" s="128"/>
+    </row>
+    <row r="44" s="1" customFormat="1" spans="1:17">
+      <c r="A44" s="2"/>
+      <c r="H44" s="68"/>
+      <c r="Q44" s="90"/>
+    </row>
+    <row r="45" s="1" customFormat="1" spans="1:17">
+      <c r="A45" s="2"/>
+      <c r="H45" s="68"/>
+      <c r="Q45" s="90"/>
     </row>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A1:R1"/>
-    <mergeCell ref="L27:O27"/>
-    <mergeCell ref="L28:O28"/>
+    <mergeCell ref="L29:O29"/>
+    <mergeCell ref="L30:O30"/>
     <mergeCell ref="B3:B7"/>
     <mergeCell ref="B9:B10"/>
-    <mergeCell ref="B11:B15"/>
-    <mergeCell ref="B17:B20"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="B23:B26"/>
+    <mergeCell ref="B11:B17"/>
+    <mergeCell ref="B19:B22"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="B25:B28"/>
   </mergeCells>
-  <conditionalFormatting sqref="Q22">
-    <cfRule type="dataBar" priority="14">
+  <conditionalFormatting sqref="Q24">
+    <cfRule type="dataBar" priority="15">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4039,13 +4203,13 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{17694de5-516d-4346-9e95-5c8155a1fa16}</x14:id>
+          <x14:id>{a7177eaa-5f93-4441-aade-07dbca551305}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L25">
-    <cfRule type="colorScale" priority="4">
+  <conditionalFormatting sqref="L27">
+    <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4055,7 +4219,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="5">
+    <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4066,8 +4230,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q25">
-    <cfRule type="dataBar" priority="2">
+  <conditionalFormatting sqref="Q27">
+    <cfRule type="dataBar" priority="3">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4075,13 +4239,13 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{23c6cca4-e70c-4329-92d6-533dea04c7e4}</x14:id>
+          <x14:id>{8ae3e078-20bf-4fab-b4d9-9a19e57eb3a1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L26">
-    <cfRule type="colorScale" priority="6">
+  <conditionalFormatting sqref="L28">
+    <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4092,8 +4256,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q26">
-    <cfRule type="dataBar" priority="3">
+  <conditionalFormatting sqref="Q28">
+    <cfRule type="dataBar" priority="4">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4101,13 +4265,13 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8430697a-44bc-4c46-94a8-75ac0eb4224a}</x14:id>
+          <x14:id>{73c16a20-6ca5-41f8-8719-298c2c627fbf}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P28">
-    <cfRule type="dataBar" priority="1">
+  <conditionalFormatting sqref="P30">
+    <cfRule type="dataBar" priority="2">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4115,13 +4279,13 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{548a632a-72f8-420c-a9be-ee5c118fc17b}</x14:id>
+          <x14:id>{a8943134-f8f0-4df3-a9a0-86442e65814b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L3:L7">
-    <cfRule type="colorScale" priority="8">
+    <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4133,6 +4297,20 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N3:N5">
+    <cfRule type="dataBar" priority="12">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{73d72061-44be-43bf-b86a-016273a3fadd}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N9:N10">
     <cfRule type="dataBar" priority="11">
       <dataBar>
         <cfvo type="min"/>
@@ -4141,12 +4319,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{250e76a0-f923-487a-abc1-d6440c0a748c}</x14:id>
+          <x14:id>{431abf7b-01d1-4562-b5f9-4f47436b3001}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N9:N10">
+  <conditionalFormatting sqref="N18:N20">
     <cfRule type="dataBar" priority="10">
       <dataBar>
         <cfvo type="min"/>
@@ -4155,13 +4333,13 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a5a3dba1-3f57-4165-841e-58c8eaa0d0ee}</x14:id>
+          <x14:id>{2d34257c-d5c6-42a5-a089-b74c0971175c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N16:N18">
-    <cfRule type="dataBar" priority="9">
+  <conditionalFormatting sqref="P3:P28">
+    <cfRule type="dataBar" priority="17">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4169,27 +4347,13 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{cbf315cd-bc48-4e61-b4c9-e69ff35f2b15}</x14:id>
+          <x14:id>{70ce0387-edb2-443c-842f-1d5ee6e70af7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P3:P26">
-    <cfRule type="dataBar" priority="16">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ae99a424-93e0-4441-ac10-7ab1aa912812}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M3:M7 L8:M24">
-    <cfRule type="colorScale" priority="15">
+  <conditionalFormatting sqref="M3:M16 L17:M26 L8:L14">
+    <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4200,8 +4364,20 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M25:M26 L26">
-    <cfRule type="colorScale" priority="7">
+  <conditionalFormatting sqref="L3:M28">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M27:M28 L28">
+    <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4223,15 +4399,17 @@
     <hyperlink ref="N13" r:id="rId8" display="LCSC"/>
     <hyperlink ref="N12" r:id="rId9" display="LCSC"/>
     <hyperlink ref="N14" r:id="rId10" display="LCSC"/>
-    <hyperlink ref="N15" r:id="rId11" display="LCSC"/>
-    <hyperlink ref="N16" r:id="rId12" display="Utsource"/>
-    <hyperlink ref="N18" r:id="rId13" display="LCSC"/>
+    <hyperlink ref="N17" r:id="rId11" display="LCSC"/>
+    <hyperlink ref="N18" r:id="rId12" display="Utsource"/>
+    <hyperlink ref="N20" r:id="rId13" display="LCSC"/>
     <hyperlink ref="N6" r:id="rId14" display="LCSC"/>
     <hyperlink ref="N7" r:id="rId15" display="LCSC"/>
-    <hyperlink ref="N19" r:id="rId16" display="Alibaba"/>
-    <hyperlink ref="N23" r:id="rId17" display="Aliexpress"/>
-    <hyperlink ref="N24" r:id="rId18" display="Aliexpress"/>
-    <hyperlink ref="N20" r:id="rId19" display="LCSC"/>
+    <hyperlink ref="N21" r:id="rId16" display="Alibaba"/>
+    <hyperlink ref="N25" r:id="rId17" display="Aliexpress"/>
+    <hyperlink ref="N26" r:id="rId18" display="Aliexpress"/>
+    <hyperlink ref="N22" r:id="rId19" display="LCSC"/>
+    <hyperlink ref="N15" r:id="rId20" display="LCSC"/>
+    <hyperlink ref="N16" r:id="rId21" display="LCSC"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -4239,7 +4417,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{17694de5-516d-4346-9e95-5c8155a1fa16}">
+          <x14:cfRule type="dataBar" id="{a7177eaa-5f93-4441-aade-07dbca551305}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -4249,10 +4427,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>Q22</xm:sqref>
+          <xm:sqref>Q24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{23c6cca4-e70c-4329-92d6-533dea04c7e4}">
+          <x14:cfRule type="dataBar" id="{8ae3e078-20bf-4fab-b4d9-9a19e57eb3a1}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -4262,10 +4440,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>Q25</xm:sqref>
+          <xm:sqref>Q27</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8430697a-44bc-4c46-94a8-75ac0eb4224a}">
+          <x14:cfRule type="dataBar" id="{73c16a20-6ca5-41f8-8719-298c2c627fbf}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -4275,10 +4453,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>Q26</xm:sqref>
+          <xm:sqref>Q28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{548a632a-72f8-420c-a9be-ee5c118fc17b}">
+          <x14:cfRule type="dataBar" id="{a8943134-f8f0-4df3-a9a0-86442e65814b}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -4288,10 +4466,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>P28</xm:sqref>
+          <xm:sqref>P30</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{250e76a0-f923-487a-abc1-d6440c0a748c}">
+          <x14:cfRule type="dataBar" id="{73d72061-44be-43bf-b86a-016273a3fadd}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -4304,7 +4482,7 @@
           <xm:sqref>N3:N5</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a5a3dba1-3f57-4165-841e-58c8eaa0d0ee}">
+          <x14:cfRule type="dataBar" id="{431abf7b-01d1-4562-b5f9-4f47436b3001}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -4317,7 +4495,7 @@
           <xm:sqref>N9:N10</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{cbf315cd-bc48-4e61-b4c9-e69ff35f2b15}">
+          <x14:cfRule type="dataBar" id="{2d34257c-d5c6-42a5-a089-b74c0971175c}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -4327,10 +4505,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>N16:N18</xm:sqref>
+          <xm:sqref>N18:N20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ae99a424-93e0-4441-ac10-7ab1aa912812}">
+          <x14:cfRule type="dataBar" id="{70ce0387-edb2-443c-842f-1d5ee6e70af7}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -4340,7 +4518,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>P3:P26</xm:sqref>
+          <xm:sqref>P3:P28</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>

--- a/Deliverables/BOM/LCSC_Control_Board.xlsx
+++ b/Deliverables/BOM/LCSC_Control_Board.xlsx
@@ -1,20 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24618"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\ChrisitanRaun-AnnanasMotor\Deliverables\BOM\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC2A59F7-A1E7-401F-8044-203FC0FFB203}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="24000" windowHeight="9795"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="170">
   <si>
     <t xml:space="preserve">Bill of Material (BOM) for Refrence Formate </t>
   </si>
@@ -383,9 +399,6 @@
     <t>Omron</t>
   </si>
   <si>
-    <t>Utsource</t>
-  </si>
-  <si>
     <t>Ics</t>
   </si>
   <si>
@@ -431,9 +444,6 @@
     <t xml:space="preserve">Infineon </t>
   </si>
   <si>
-    <t>Alibaba</t>
-  </si>
-  <si>
     <t>IC TRNSLTR BIDIRECTIONAL US8</t>
   </si>
   <si>
@@ -464,9 +474,6 @@
     <t>C3E-25.000-8-1015-X-M</t>
   </si>
   <si>
-    <t>out of stock</t>
-  </si>
-  <si>
     <t>Crystal 32.768KHZ 6.0PF SMD</t>
   </si>
   <si>
@@ -534,24 +541,22 @@
   </si>
   <si>
     <t>Single Board Cost</t>
+  </si>
+  <si>
+    <t>Awaiting Custom Supplier Quotation</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="9">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="&quot;$&quot;#,##0.0000"/>
-    <numFmt numFmtId="179" formatCode="&quot;$&quot;#,##0.00000"/>
-    <numFmt numFmtId="180" formatCode="&quot;$&quot;#,##0.0000_);[Red]\(&quot;$&quot;#,##0.0000\)"/>
-    <numFmt numFmtId="181" formatCode="&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="182" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="4">
+    <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.0000"/>
+    <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00000"/>
+    <numFmt numFmtId="169" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="170" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
   </numFmts>
-  <fonts count="39">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -609,13 +614,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF444444"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <strike/>
       <sz val="10"/>
       <color rgb="FFFF0000"/>
@@ -648,7 +646,6 @@
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -662,7 +659,6 @@
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
-      <charset val="0"/>
     </font>
     <font>
       <sz val="10"/>
@@ -695,147 +691,10 @@
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="40">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -844,7 +703,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="1" tint="0.5"/>
+        <fgColor theme="1" tint="0.499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -868,7 +727,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.6"/>
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -884,194 +743,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="39">
+  <borders count="31">
     <border>
       <left/>
       <right/>
@@ -1479,255 +1152,16 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="34" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="35" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="33" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="35" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="37" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="29" borderId="36" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="9" borderId="36" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="38" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="32" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="144">
+  <cellXfs count="160">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1735,12 +1169,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1753,15 +1181,6 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1770,12 +1189,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1783,24 +1196,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1811,12 +1209,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1831,47 +1223,20 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1882,52 +1247,34 @@
     <xf numFmtId="0" fontId="7" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1936,167 +1283,125 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="1" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="12" fillId="0" borderId="8" xfId="7" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="12" fillId="0" borderId="11" xfId="7" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="6" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="12" fillId="0" borderId="14" xfId="7" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="11" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="6" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="1" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="12" fillId="0" borderId="16" xfId="7" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="12" fillId="4" borderId="8" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="4" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="12" fillId="4" borderId="11" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="14" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="14" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="11" fillId="4" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="4" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="13" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="8" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="6" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="14" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="4" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="8" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="6" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="11" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="9" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="9" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="4" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="181" fontId="4" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2105,246 +1410,245 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="4" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="181" fontId="4" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="4" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="4" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="4" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="4" fillId="6" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="19" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="19" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="4" fillId="7" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="19" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="4" fillId="7" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="6" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="18" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="18" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="7" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="18" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="7" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="11" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="11" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="14" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="14" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="11" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="19" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="40% - Accent1" xfId="1" builtinId="31"/>
-    <cellStyle name="Comma" xfId="2" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="3" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
-    <cellStyle name="Currency" xfId="5" builtinId="4"/>
-    <cellStyle name="Percent" xfId="6" builtinId="5"/>
-    <cellStyle name="Hyperlink" xfId="7" builtinId="8"/>
-    <cellStyle name="60% - Accent4" xfId="8" builtinId="44"/>
-    <cellStyle name="Followed Hyperlink" xfId="9" builtinId="9"/>
-    <cellStyle name="Check Cell" xfId="10" builtinId="23"/>
-    <cellStyle name="Heading 2" xfId="11" builtinId="17"/>
-    <cellStyle name="Note" xfId="12" builtinId="10"/>
-    <cellStyle name="40% - Accent3" xfId="13" builtinId="39"/>
-    <cellStyle name="Warning Text" xfId="14" builtinId="11"/>
-    <cellStyle name="40% - Accent2" xfId="15" builtinId="35"/>
-    <cellStyle name="Title" xfId="16" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="17" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="18" builtinId="16"/>
-    <cellStyle name="Heading 3" xfId="19" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="20" builtinId="19"/>
-    <cellStyle name="Input" xfId="21" builtinId="20"/>
-    <cellStyle name="60% - Accent3" xfId="22" builtinId="40"/>
-    <cellStyle name="Good" xfId="23" builtinId="26"/>
-    <cellStyle name="Output" xfId="24" builtinId="21"/>
-    <cellStyle name="20% - Accent1" xfId="25" builtinId="30"/>
-    <cellStyle name="Calculation" xfId="26" builtinId="22"/>
-    <cellStyle name="Linked Cell" xfId="27" builtinId="24"/>
-    <cellStyle name="Total" xfId="28" builtinId="25"/>
-    <cellStyle name="Bad" xfId="29" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="30" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="31" builtinId="29"/>
-    <cellStyle name="20% - Accent5" xfId="32" builtinId="46"/>
-    <cellStyle name="60% - Accent1" xfId="33" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="34" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="35" builtinId="34"/>
-    <cellStyle name="20% - Accent6" xfId="36" builtinId="50"/>
-    <cellStyle name="60% - Accent2" xfId="37" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="38" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="39" builtinId="38"/>
-    <cellStyle name="Accent4" xfId="40" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="41" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="42" builtinId="43"/>
-    <cellStyle name="Accent5" xfId="43" builtinId="45"/>
-    <cellStyle name="40% - Accent5" xfId="44" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="45" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="46" builtinId="49"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2602,1585 +1906,1580 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AH45"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="6.14285714285714" style="2" customWidth="1"/>
-    <col min="2" max="2" width="14.4285714285714" style="1" customWidth="1"/>
-    <col min="3" max="3" width="47.5714285714286" style="1" customWidth="1"/>
-    <col min="4" max="4" width="33.1428571428571" style="1" customWidth="1"/>
+    <col min="1" max="1" width="6.109375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="14.44140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="47.5546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="33.109375" style="1" customWidth="1"/>
     <col min="5" max="5" width="21" style="1" customWidth="1"/>
-    <col min="6" max="6" width="36.2857142857143" style="1" customWidth="1"/>
-    <col min="7" max="7" width="19.1428571428571" style="1" customWidth="1"/>
-    <col min="8" max="8" width="14.4285714285714" style="2" customWidth="1"/>
-    <col min="9" max="9" width="21.5714285714286" style="1" customWidth="1"/>
+    <col min="6" max="6" width="34.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.109375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="14.44140625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="21.5546875" style="1" customWidth="1"/>
     <col min="10" max="10" width="7" style="1" customWidth="1"/>
-    <col min="11" max="11" width="11.5714285714286" style="1" customWidth="1"/>
-    <col min="12" max="12" width="21.8571428571429" style="1" customWidth="1"/>
-    <col min="13" max="13" width="14.1428571428571" style="1" customWidth="1"/>
-    <col min="14" max="14" width="10.2857142857143" style="1" customWidth="1"/>
-    <col min="15" max="15" width="12.7142857142857" style="1" customWidth="1"/>
-    <col min="16" max="16" width="13.4285714285714" style="1" customWidth="1"/>
-    <col min="17" max="17" width="14.1428571428571" style="1" customWidth="1"/>
-    <col min="18" max="18" width="26.5714285714286" style="1" customWidth="1"/>
+    <col min="11" max="11" width="11.5546875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="21.88671875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="14.109375" style="1" customWidth="1"/>
+    <col min="14" max="14" width="13.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.6640625" style="1" customWidth="1"/>
+    <col min="16" max="16" width="13.44140625" style="1" customWidth="1"/>
+    <col min="17" max="17" width="14.109375" style="1" customWidth="1"/>
+    <col min="18" max="18" width="29.88671875" style="1" bestFit="1" customWidth="1"/>
     <col min="19" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="16.5" spans="1:34">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:34" ht="15.6">
+      <c r="A1" s="146" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4"/>
-      <c r="N1" s="4"/>
-      <c r="O1" s="4"/>
-      <c r="P1" s="4"/>
-      <c r="Q1" s="4"/>
-      <c r="R1" s="4"/>
-      <c r="S1" s="125"/>
-      <c r="T1" s="125"/>
-      <c r="U1" s="125"/>
-      <c r="V1" s="125"/>
-      <c r="W1" s="125"/>
-      <c r="X1" s="125"/>
-      <c r="Y1" s="125"/>
-      <c r="Z1" s="125"/>
-      <c r="AA1" s="125"/>
-      <c r="AB1" s="125"/>
-      <c r="AC1" s="125"/>
-      <c r="AD1" s="125"/>
-      <c r="AE1" s="125"/>
-      <c r="AF1" s="125"/>
-      <c r="AG1" s="125"/>
-      <c r="AH1" s="143"/>
-    </row>
-    <row r="2" s="1" customFormat="1" ht="32.25" spans="1:18">
-      <c r="A2" s="5" t="s">
+      <c r="B1" s="147"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="147"/>
+      <c r="G1" s="147"/>
+      <c r="H1" s="147"/>
+      <c r="I1" s="147"/>
+      <c r="J1" s="147"/>
+      <c r="K1" s="147"/>
+      <c r="L1" s="147"/>
+      <c r="M1" s="147"/>
+      <c r="N1" s="147"/>
+      <c r="O1" s="147"/>
+      <c r="P1" s="147"/>
+      <c r="Q1" s="147"/>
+      <c r="R1" s="147"/>
+      <c r="S1" s="82"/>
+      <c r="T1" s="82"/>
+      <c r="U1" s="82"/>
+      <c r="V1" s="82"/>
+      <c r="W1" s="82"/>
+      <c r="X1" s="82"/>
+      <c r="Y1" s="82"/>
+      <c r="Z1" s="82"/>
+      <c r="AA1" s="82"/>
+      <c r="AB1" s="82"/>
+      <c r="AC1" s="82"/>
+      <c r="AD1" s="82"/>
+      <c r="AE1" s="82"/>
+      <c r="AF1" s="82"/>
+      <c r="AG1" s="82"/>
+      <c r="AH1" s="100"/>
+    </row>
+    <row r="2" spans="1:34" ht="31.2">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="I2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="J2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="7" t="s">
+      <c r="K2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="7" t="s">
+      <c r="L2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="M2" s="7" t="s">
+      <c r="M2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="N2" s="69" t="s">
+      <c r="N2" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="O2" s="70" t="s">
+      <c r="O2" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="P2" s="7" t="s">
+      <c r="P2" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="Q2" s="7" t="s">
+      <c r="Q2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="R2" s="126" t="s">
+      <c r="R2" s="83" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="15.75" spans="1:19">
-      <c r="A3" s="8">
+    <row r="3" spans="1:34">
+      <c r="A3" s="6">
         <v>1</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="151" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="144" t="s">
+      <c r="C3" s="101" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="145" t="s">
+      <c r="D3" s="102" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="146" t="s">
+      <c r="E3" s="103" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="146" t="s">
+      <c r="F3" s="103" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="147" t="s">
+      <c r="G3" s="104" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="14" t="s">
+      <c r="H3" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="148" t="s">
+      <c r="I3" s="105" t="s">
         <v>26</v>
       </c>
-      <c r="J3" s="146" t="s">
+      <c r="J3" s="103" t="s">
         <v>27</v>
       </c>
-      <c r="K3" s="12">
+      <c r="K3" s="7">
         <v>1620</v>
       </c>
-      <c r="L3" s="12">
+      <c r="L3" s="7">
         <v>4</v>
       </c>
-      <c r="M3" s="12">
+      <c r="M3" s="7">
         <f t="shared" ref="M3:M18" si="0">L3*400</f>
         <v>1600</v>
       </c>
-      <c r="N3" s="71" t="s">
+      <c r="N3" s="42" t="s">
         <v>28</v>
       </c>
-      <c r="O3" s="72">
-        <v>0.0682</v>
-      </c>
-      <c r="P3" s="73">
+      <c r="O3" s="43">
+        <v>6.8199999999999997E-2</v>
+      </c>
+      <c r="P3" s="44">
         <f t="shared" ref="P3:P16" si="1">O3*K3</f>
-        <v>110.484</v>
-      </c>
-      <c r="Q3" s="12"/>
-      <c r="R3" s="127"/>
-      <c r="S3" s="128"/>
-    </row>
-    <row r="4" s="1" customFormat="1" ht="51.75" spans="1:19">
-      <c r="A4" s="8">
+        <v>110.48399999999999</v>
+      </c>
+      <c r="Q3" s="7"/>
+      <c r="R3" s="84"/>
+      <c r="S3" s="85"/>
+    </row>
+    <row r="4" spans="1:34" ht="55.2">
+      <c r="A4" s="6">
         <v>2</v>
       </c>
-      <c r="B4" s="15"/>
-      <c r="C4" s="149" t="s">
+      <c r="B4" s="152"/>
+      <c r="C4" s="106" t="s">
         <v>29</v>
       </c>
-      <c r="D4" s="17" t="s">
+      <c r="D4" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="E4" s="150" t="s">
+      <c r="E4" s="107" t="s">
         <v>31</v>
       </c>
-      <c r="F4" s="150" t="s">
+      <c r="F4" s="107" t="s">
         <v>32</v>
       </c>
-      <c r="G4" s="151" t="s">
+      <c r="G4" s="108" t="s">
         <v>33</v>
       </c>
-      <c r="H4" s="20" t="s">
+      <c r="H4" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="I4" s="152" t="s">
+      <c r="I4" s="109" t="s">
         <v>26</v>
       </c>
-      <c r="J4" s="150" t="s">
+      <c r="J4" s="107" t="s">
         <v>35</v>
       </c>
-      <c r="K4" s="18">
+      <c r="K4" s="11">
         <v>8850</v>
       </c>
-      <c r="L4" s="18">
+      <c r="L4" s="11">
         <v>24</v>
       </c>
-      <c r="M4" s="18">
+      <c r="M4" s="11">
         <f t="shared" si="0"/>
         <v>9600</v>
       </c>
-      <c r="N4" s="74" t="s">
+      <c r="N4" s="45" t="s">
         <v>28</v>
       </c>
-      <c r="O4" s="75">
-        <v>0.0047</v>
-      </c>
-      <c r="P4" s="76">
+      <c r="O4" s="46">
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="P4" s="47">
         <f t="shared" si="1"/>
-        <v>41.595</v>
-      </c>
-      <c r="Q4" s="18"/>
-      <c r="R4" s="129"/>
-      <c r="S4" s="128"/>
-    </row>
-    <row r="5" s="1" customFormat="1" ht="15.75" spans="1:19">
-      <c r="A5" s="8">
+        <v>41.594999999999999</v>
+      </c>
+      <c r="Q4" s="11"/>
+      <c r="R4" s="86"/>
+      <c r="S4" s="85"/>
+    </row>
+    <row r="5" spans="1:34">
+      <c r="A5" s="6">
         <v>3</v>
       </c>
-      <c r="B5" s="15"/>
-      <c r="C5" s="149" t="s">
+      <c r="B5" s="152"/>
+      <c r="C5" s="106" t="s">
         <v>36</v>
       </c>
-      <c r="D5" s="153" t="s">
+      <c r="D5" s="110" t="s">
         <v>37</v>
       </c>
-      <c r="E5" s="150" t="s">
+      <c r="E5" s="107" t="s">
         <v>22</v>
       </c>
-      <c r="F5" s="150" t="s">
+      <c r="F5" s="107" t="s">
         <v>38</v>
       </c>
-      <c r="G5" s="151" t="s">
+      <c r="G5" s="108" t="s">
         <v>24</v>
       </c>
-      <c r="H5" s="20" t="s">
+      <c r="H5" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="I5" s="154" t="s">
+      <c r="I5" s="111" t="s">
         <v>40</v>
       </c>
-      <c r="J5" s="150" t="s">
+      <c r="J5" s="107" t="s">
         <v>41</v>
       </c>
-      <c r="K5" s="18">
+      <c r="K5" s="11">
         <v>420</v>
       </c>
-      <c r="L5" s="18">
+      <c r="L5" s="11">
         <v>1</v>
       </c>
-      <c r="M5" s="18">
+      <c r="M5" s="11">
         <f t="shared" si="0"/>
         <v>400</v>
       </c>
-      <c r="N5" s="74" t="s">
+      <c r="N5" s="45" t="s">
         <v>28</v>
       </c>
-      <c r="O5" s="75">
-        <v>0.087</v>
-      </c>
-      <c r="P5" s="76">
+      <c r="O5" s="46">
+        <v>8.6999999999999994E-2</v>
+      </c>
+      <c r="P5" s="47">
         <f t="shared" si="1"/>
         <v>36.54</v>
       </c>
-      <c r="Q5" s="18"/>
-      <c r="R5" s="129"/>
-      <c r="S5" s="128"/>
-    </row>
-    <row r="6" s="1" customFormat="1" ht="15.75" spans="1:19">
-      <c r="A6" s="8">
+      <c r="Q5" s="11"/>
+      <c r="R5" s="86"/>
+      <c r="S5" s="85"/>
+    </row>
+    <row r="6" spans="1:34">
+      <c r="A6" s="6">
         <v>4</v>
       </c>
-      <c r="B6" s="15"/>
-      <c r="C6" s="149" t="s">
+      <c r="B6" s="152"/>
+      <c r="C6" s="106" t="s">
         <v>42</v>
       </c>
-      <c r="D6" s="153" t="s">
+      <c r="D6" s="110" t="s">
         <v>43</v>
       </c>
-      <c r="E6" s="150" t="s">
+      <c r="E6" s="107" t="s">
         <v>31</v>
       </c>
-      <c r="F6" s="150" t="s">
+      <c r="F6" s="107" t="s">
         <v>44</v>
       </c>
-      <c r="G6" s="151" t="s">
+      <c r="G6" s="108" t="s">
         <v>45</v>
       </c>
-      <c r="H6" s="20" t="s">
+      <c r="H6" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="I6" s="154" t="s">
+      <c r="I6" s="111" t="s">
         <v>47</v>
       </c>
-      <c r="J6" s="150" t="s">
+      <c r="J6" s="107" t="s">
         <v>48</v>
       </c>
-      <c r="K6" s="18">
+      <c r="K6" s="11">
         <v>1220</v>
       </c>
-      <c r="L6" s="18">
+      <c r="L6" s="11">
         <v>3</v>
       </c>
-      <c r="M6" s="18">
+      <c r="M6" s="11">
         <f t="shared" si="0"/>
         <v>1200</v>
       </c>
-      <c r="N6" s="155" t="s">
+      <c r="N6" s="112" t="s">
         <v>28</v>
       </c>
-      <c r="O6" s="78">
-        <v>0.0231</v>
-      </c>
-      <c r="P6" s="76">
+      <c r="O6" s="48">
+        <v>2.3099999999999999E-2</v>
+      </c>
+      <c r="P6" s="47">
         <f t="shared" si="1"/>
-        <v>28.182</v>
-      </c>
-      <c r="Q6" s="18"/>
-      <c r="R6" s="129"/>
-      <c r="S6" s="128"/>
-    </row>
-    <row r="7" s="1" customFormat="1" ht="15.75" spans="1:19">
-      <c r="A7" s="8">
+        <v>28.181999999999999</v>
+      </c>
+      <c r="Q6" s="11"/>
+      <c r="R6" s="86"/>
+      <c r="S6" s="85"/>
+    </row>
+    <row r="7" spans="1:34" ht="15" thickBot="1">
+      <c r="A7" s="6">
         <v>5</v>
       </c>
-      <c r="B7" s="22"/>
-      <c r="C7" s="156" t="s">
+      <c r="B7" s="153"/>
+      <c r="C7" s="113" t="s">
         <v>49</v>
       </c>
-      <c r="D7" s="157" t="s">
+      <c r="D7" s="114" t="s">
         <v>50</v>
       </c>
-      <c r="E7" s="158" t="s">
+      <c r="E7" s="115" t="s">
         <v>31</v>
       </c>
-      <c r="F7" s="158" t="s">
+      <c r="F7" s="115" t="s">
         <v>51</v>
       </c>
-      <c r="G7" s="159" t="s">
+      <c r="G7" s="116" t="s">
         <v>52</v>
       </c>
-      <c r="H7" s="27" t="s">
+      <c r="H7" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="I7" s="160" t="s">
+      <c r="I7" s="117" t="s">
         <v>54</v>
       </c>
-      <c r="J7" s="158" t="s">
+      <c r="J7" s="115" t="s">
         <v>55</v>
       </c>
-      <c r="K7" s="25">
+      <c r="K7" s="13">
         <v>1650</v>
       </c>
-      <c r="L7" s="25">
+      <c r="L7" s="13">
         <v>4</v>
       </c>
-      <c r="M7" s="25">
+      <c r="M7" s="13">
         <f t="shared" si="0"/>
         <v>1600</v>
       </c>
-      <c r="N7" s="161" t="s">
+      <c r="N7" s="118" t="s">
         <v>28</v>
       </c>
-      <c r="O7" s="80">
-        <v>0.0024</v>
-      </c>
-      <c r="P7" s="81">
+      <c r="O7" s="49">
+        <v>2.3999999999999998E-3</v>
+      </c>
+      <c r="P7" s="50">
         <f t="shared" si="1"/>
-        <v>3.96</v>
-      </c>
-      <c r="Q7" s="130"/>
-      <c r="R7" s="131"/>
-      <c r="S7" s="128"/>
-    </row>
-    <row r="8" s="1" customFormat="1" ht="15.75" spans="1:19">
-      <c r="A8" s="8">
+        <v>3.9599999999999995</v>
+      </c>
+      <c r="Q7" s="87"/>
+      <c r="R7" s="88"/>
+      <c r="S7" s="85"/>
+    </row>
+    <row r="8" spans="1:34" ht="15" thickBot="1">
+      <c r="A8" s="6">
         <v>6</v>
       </c>
-      <c r="B8" s="28" t="s">
+      <c r="B8" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="C8" s="162" t="s">
+      <c r="C8" s="119" t="s">
         <v>57</v>
       </c>
-      <c r="D8" s="163" t="s">
+      <c r="D8" s="120" t="s">
         <v>58</v>
       </c>
-      <c r="E8" s="164" t="s">
+      <c r="E8" s="121" t="s">
         <v>59</v>
       </c>
-      <c r="F8" s="164" t="s">
+      <c r="F8" s="121" t="s">
         <v>60</v>
       </c>
-      <c r="G8" s="165" t="s">
+      <c r="G8" s="122" t="s">
         <v>61</v>
       </c>
-      <c r="H8" s="33" t="s">
+      <c r="H8" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="I8" s="166" t="s">
+      <c r="I8" s="123" t="s">
         <v>26</v>
       </c>
-      <c r="J8" s="165" t="s">
+      <c r="J8" s="122" t="s">
         <v>63</v>
       </c>
-      <c r="K8" s="32">
+      <c r="K8" s="18">
         <v>1220</v>
       </c>
-      <c r="L8" s="31">
+      <c r="L8" s="17">
         <v>3</v>
       </c>
-      <c r="M8" s="31">
+      <c r="M8" s="17">
         <f t="shared" si="0"/>
         <v>1200</v>
       </c>
-      <c r="N8" s="167" t="s">
+      <c r="N8" s="124" t="s">
         <v>28</v>
       </c>
-      <c r="O8" s="83">
-        <v>0.045</v>
-      </c>
-      <c r="P8" s="84">
+      <c r="O8" s="51">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="P8" s="52">
         <f t="shared" si="1"/>
         <v>54.9</v>
       </c>
-      <c r="Q8" s="31"/>
-      <c r="R8" s="132"/>
-      <c r="S8" s="128"/>
-    </row>
-    <row r="9" s="1" customFormat="1" ht="15.75" spans="1:19">
-      <c r="A9" s="8">
+      <c r="Q8" s="17"/>
+      <c r="R8" s="89"/>
+      <c r="S8" s="85"/>
+    </row>
+    <row r="9" spans="1:34" ht="15" thickBot="1">
+      <c r="A9" s="6">
         <v>7</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="151" t="s">
         <v>64</v>
       </c>
-      <c r="C9" s="144" t="s">
+      <c r="C9" s="101" t="s">
         <v>65</v>
       </c>
-      <c r="D9" s="145" t="s">
+      <c r="D9" s="102" t="s">
         <v>66</v>
       </c>
-      <c r="E9" s="146" t="s">
+      <c r="E9" s="103" t="s">
         <v>67</v>
       </c>
-      <c r="F9" s="146" t="s">
+      <c r="F9" s="103" t="s">
         <v>68</v>
       </c>
-      <c r="G9" s="147" t="s">
+      <c r="G9" s="104" t="s">
         <v>69</v>
       </c>
-      <c r="H9" s="14" t="s">
+      <c r="H9" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="I9" s="168" t="s">
+      <c r="I9" s="125" t="s">
         <v>26</v>
       </c>
-      <c r="J9" s="147" t="s">
+      <c r="J9" s="104" t="s">
         <v>63</v>
       </c>
-      <c r="K9" s="13">
+      <c r="K9" s="8">
         <v>2100</v>
       </c>
-      <c r="L9" s="12">
+      <c r="L9" s="7">
         <v>5</v>
       </c>
-      <c r="M9" s="12">
+      <c r="M9" s="7">
         <f t="shared" si="0"/>
         <v>2000</v>
       </c>
-      <c r="N9" s="71" t="s">
+      <c r="N9" s="42" t="s">
         <v>28</v>
       </c>
-      <c r="O9" s="72">
-        <v>0.0052</v>
-      </c>
-      <c r="P9" s="73">
+      <c r="O9" s="43">
+        <v>5.1999999999999998E-3</v>
+      </c>
+      <c r="P9" s="44">
         <f t="shared" si="1"/>
         <v>10.92</v>
       </c>
-      <c r="Q9" s="12"/>
-      <c r="R9" s="127"/>
-      <c r="S9" s="128"/>
-    </row>
-    <row r="10" s="1" customFormat="1" ht="15.75" spans="1:19">
-      <c r="A10" s="8">
+      <c r="Q9" s="7"/>
+      <c r="R9" s="84"/>
+      <c r="S9" s="85"/>
+    </row>
+    <row r="10" spans="1:34">
+      <c r="A10" s="6">
         <v>8</v>
       </c>
-      <c r="B10" s="22"/>
-      <c r="C10" s="156" t="s">
+      <c r="B10" s="153"/>
+      <c r="C10" s="113" t="s">
         <v>71</v>
       </c>
-      <c r="D10" s="157" t="s">
+      <c r="D10" s="114" t="s">
         <v>72</v>
       </c>
-      <c r="E10" s="158" t="s">
+      <c r="E10" s="115" t="s">
         <v>73</v>
       </c>
-      <c r="F10" s="158" t="s">
+      <c r="F10" s="115" t="s">
         <v>74</v>
       </c>
-      <c r="G10" s="159" t="s">
+      <c r="G10" s="116" t="s">
         <v>75</v>
       </c>
-      <c r="H10" s="27" t="s">
+      <c r="H10" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="I10" s="160" t="s">
+      <c r="I10" s="117" t="s">
         <v>26</v>
       </c>
-      <c r="J10" s="159" t="s">
+      <c r="J10" s="116" t="s">
         <v>63</v>
       </c>
-      <c r="K10" s="26">
+      <c r="K10" s="14">
         <v>420</v>
       </c>
-      <c r="L10" s="25">
+      <c r="L10" s="13">
         <v>1</v>
       </c>
-      <c r="M10" s="25">
+      <c r="M10" s="13">
         <f t="shared" si="0"/>
         <v>400</v>
       </c>
-      <c r="N10" s="85" t="s">
+      <c r="N10" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="O10" s="86">
-        <v>0.0379</v>
-      </c>
-      <c r="P10" s="81">
+      <c r="O10" s="54">
+        <v>3.7900000000000003E-2</v>
+      </c>
+      <c r="P10" s="50">
         <f t="shared" si="1"/>
-        <v>15.918</v>
-      </c>
-      <c r="Q10" s="25"/>
-      <c r="R10" s="131"/>
-      <c r="S10" s="128"/>
-    </row>
-    <row r="11" s="1" customFormat="1" ht="26.25" spans="1:19">
-      <c r="A11" s="8">
+        <v>15.918000000000001</v>
+      </c>
+      <c r="Q10" s="13"/>
+      <c r="R10" s="88"/>
+      <c r="S10" s="85"/>
+    </row>
+    <row r="11" spans="1:34" ht="27.6">
+      <c r="A11" s="6">
         <v>9</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="151" t="s">
         <v>77</v>
       </c>
-      <c r="C11" s="144" t="s">
+      <c r="C11" s="101" t="s">
         <v>78</v>
       </c>
-      <c r="D11" s="34" t="s">
+      <c r="D11" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="E11" s="146" t="s">
+      <c r="E11" s="103" t="s">
         <v>80</v>
       </c>
-      <c r="F11" s="146" t="s">
+      <c r="F11" s="103" t="s">
         <v>81</v>
       </c>
-      <c r="G11" s="147" t="s">
+      <c r="G11" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="H11" s="14" t="s">
+      <c r="H11" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="I11" s="168" t="s">
+      <c r="I11" s="125" t="s">
         <v>26</v>
       </c>
-      <c r="J11" s="146" t="s">
+      <c r="J11" s="103" t="s">
         <v>83</v>
       </c>
-      <c r="K11" s="44">
+      <c r="K11" s="24">
         <v>4900</v>
       </c>
-      <c r="L11" s="12">
+      <c r="L11" s="7">
         <v>12</v>
       </c>
-      <c r="M11" s="12">
+      <c r="M11" s="7">
         <f t="shared" si="0"/>
         <v>4800</v>
       </c>
-      <c r="N11" s="169" t="s">
+      <c r="N11" s="126" t="s">
         <v>28</v>
       </c>
-      <c r="O11" s="72">
-        <v>0.0011</v>
-      </c>
-      <c r="P11" s="73">
+      <c r="O11" s="43">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="P11" s="44">
         <f t="shared" si="1"/>
-        <v>5.39</v>
-      </c>
-      <c r="Q11" s="12"/>
-      <c r="R11" s="127"/>
-      <c r="S11" s="128"/>
-    </row>
-    <row r="12" s="1" customFormat="1" ht="15.75" spans="1:19">
-      <c r="A12" s="8">
+        <v>5.3900000000000006</v>
+      </c>
+      <c r="Q11" s="7"/>
+      <c r="R11" s="84"/>
+      <c r="S11" s="85"/>
+    </row>
+    <row r="12" spans="1:34">
+      <c r="A12" s="6">
         <v>10</v>
       </c>
-      <c r="B12" s="15"/>
-      <c r="C12" s="149" t="s">
+      <c r="B12" s="152"/>
+      <c r="C12" s="106" t="s">
         <v>84</v>
       </c>
-      <c r="D12" s="153" t="s">
+      <c r="D12" s="110" t="s">
         <v>85</v>
       </c>
-      <c r="E12" s="150" t="s">
+      <c r="E12" s="107" t="s">
         <v>80</v>
       </c>
-      <c r="F12" s="150" t="s">
+      <c r="F12" s="107" t="s">
         <v>86</v>
       </c>
-      <c r="G12" s="151" t="s">
+      <c r="G12" s="108" t="s">
         <v>33</v>
       </c>
-      <c r="H12" s="20" t="s">
+      <c r="H12" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="I12" s="154" t="s">
+      <c r="I12" s="111" t="s">
         <v>26</v>
       </c>
-      <c r="J12" s="150" t="s">
+      <c r="J12" s="107" t="s">
         <v>88</v>
       </c>
-      <c r="K12" s="47">
+      <c r="K12" s="25">
         <v>1300</v>
       </c>
-      <c r="L12" s="18">
+      <c r="L12" s="11">
         <v>3</v>
       </c>
-      <c r="M12" s="18">
+      <c r="M12" s="11">
         <f t="shared" si="0"/>
         <v>1200</v>
       </c>
-      <c r="N12" s="155" t="s">
+      <c r="N12" s="112" t="s">
         <v>28</v>
       </c>
-      <c r="O12" s="75">
-        <v>0.0011</v>
-      </c>
-      <c r="P12" s="76">
+      <c r="O12" s="46">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="P12" s="47">
         <f t="shared" si="1"/>
-        <v>1.43</v>
-      </c>
-      <c r="Q12" s="18"/>
-      <c r="R12" s="129"/>
-      <c r="S12" s="128"/>
-    </row>
-    <row r="13" s="1" customFormat="1" ht="15.75" spans="1:19">
-      <c r="A13" s="8">
+        <v>1.4300000000000002</v>
+      </c>
+      <c r="Q12" s="11"/>
+      <c r="R12" s="86"/>
+      <c r="S12" s="85"/>
+    </row>
+    <row r="13" spans="1:34">
+      <c r="A13" s="6">
         <v>11</v>
       </c>
-      <c r="B13" s="15"/>
-      <c r="C13" s="149" t="s">
+      <c r="B13" s="152"/>
+      <c r="C13" s="106" t="s">
         <v>89</v>
       </c>
-      <c r="D13" s="153" t="s">
+      <c r="D13" s="110" t="s">
         <v>90</v>
       </c>
-      <c r="E13" s="150" t="s">
+      <c r="E13" s="107" t="s">
         <v>80</v>
       </c>
-      <c r="F13" s="150" t="s">
+      <c r="F13" s="107" t="s">
         <v>91</v>
       </c>
-      <c r="G13" s="151" t="s">
+      <c r="G13" s="108" t="s">
         <v>33</v>
       </c>
-      <c r="H13" s="20" t="s">
+      <c r="H13" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="I13" s="154" t="s">
+      <c r="I13" s="111" t="s">
         <v>26</v>
       </c>
-      <c r="J13" s="150" t="s">
+      <c r="J13" s="107" t="s">
         <v>93</v>
       </c>
-      <c r="K13" s="47">
+      <c r="K13" s="25">
         <v>500</v>
       </c>
-      <c r="L13" s="18">
+      <c r="L13" s="11">
         <v>1</v>
       </c>
-      <c r="M13" s="18">
+      <c r="M13" s="11">
         <f t="shared" si="0"/>
         <v>400</v>
       </c>
-      <c r="N13" s="170" t="s">
+      <c r="N13" s="127" t="s">
         <v>28</v>
       </c>
-      <c r="O13" s="89">
-        <v>0.0012</v>
-      </c>
-      <c r="P13" s="76">
+      <c r="O13" s="55">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="P13" s="47">
         <f t="shared" si="1"/>
         <v>0.6</v>
       </c>
-      <c r="Q13" s="47"/>
-      <c r="R13" s="129"/>
-      <c r="S13" s="128"/>
-    </row>
-    <row r="14" s="1" customFormat="1" ht="15.75" spans="1:19">
-      <c r="A14" s="8">
+      <c r="Q13" s="25"/>
+      <c r="R13" s="86"/>
+      <c r="S13" s="85"/>
+    </row>
+    <row r="14" spans="1:34">
+      <c r="A14" s="6">
         <v>12</v>
       </c>
-      <c r="B14" s="15"/>
-      <c r="C14" s="149" t="s">
+      <c r="B14" s="152"/>
+      <c r="C14" s="106" t="s">
         <v>94</v>
       </c>
-      <c r="D14" s="153" t="s">
+      <c r="D14" s="110" t="s">
         <v>95</v>
       </c>
-      <c r="E14" s="150" t="s">
+      <c r="E14" s="107" t="s">
         <v>80</v>
       </c>
-      <c r="F14" s="150" t="s">
+      <c r="F14" s="107" t="s">
         <v>96</v>
       </c>
-      <c r="G14" s="151" t="s">
+      <c r="G14" s="108" t="s">
         <v>33</v>
       </c>
-      <c r="H14" s="20" t="s">
+      <c r="H14" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="I14" s="154" t="s">
+      <c r="I14" s="111" t="s">
         <v>26</v>
       </c>
-      <c r="J14" s="150" t="s">
+      <c r="J14" s="107" t="s">
         <v>98</v>
       </c>
-      <c r="K14" s="47">
+      <c r="K14" s="25">
         <v>1300</v>
       </c>
-      <c r="L14" s="18">
+      <c r="L14" s="11">
         <v>4</v>
       </c>
-      <c r="M14" s="18">
+      <c r="M14" s="11">
         <f t="shared" si="0"/>
         <v>1600</v>
       </c>
-      <c r="N14" s="155" t="s">
+      <c r="N14" s="112" t="s">
         <v>28</v>
       </c>
-      <c r="O14" s="75">
-        <v>0.001</v>
-      </c>
-      <c r="P14" s="76">
+      <c r="O14" s="46">
+        <v>1E-3</v>
+      </c>
+      <c r="P14" s="47">
         <f t="shared" si="1"/>
         <v>1.3</v>
       </c>
-      <c r="Q14" s="18"/>
-      <c r="R14" s="129"/>
-      <c r="S14" s="128"/>
-    </row>
-    <row r="15" s="1" customFormat="1" ht="15.75" spans="1:19">
-      <c r="A15" s="8">
+      <c r="Q14" s="11"/>
+      <c r="R14" s="86"/>
+      <c r="S14" s="85"/>
+    </row>
+    <row r="15" spans="1:34">
+      <c r="A15" s="6">
         <v>13</v>
       </c>
-      <c r="B15" s="35"/>
-      <c r="C15" s="36" t="s">
+      <c r="B15" s="154"/>
+      <c r="C15" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="D15" s="37" t="s">
+      <c r="D15" s="22" t="s">
         <v>100</v>
       </c>
-      <c r="E15" s="37" t="s">
+      <c r="E15" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="F15" s="37" t="s">
+      <c r="F15" s="22" t="s">
         <v>101</v>
       </c>
-      <c r="G15" s="151" t="s">
+      <c r="G15" s="108" t="s">
         <v>33</v>
       </c>
-      <c r="H15" s="38" t="s">
+      <c r="H15" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="I15" s="90"/>
-      <c r="J15" s="91" t="s">
+      <c r="I15" s="111" t="s">
+        <v>26</v>
+      </c>
+      <c r="J15" s="159" t="s">
         <v>103</v>
       </c>
-      <c r="K15" s="92">
+      <c r="K15" s="57">
         <v>900</v>
       </c>
-      <c r="L15" s="37">
+      <c r="L15" s="22">
         <v>2</v>
       </c>
-      <c r="M15" s="18">
+      <c r="M15" s="11">
         <f t="shared" si="0"/>
         <v>800</v>
       </c>
-      <c r="N15" s="93" t="s">
+      <c r="N15" s="58" t="s">
         <v>28</v>
       </c>
-      <c r="O15" s="94">
-        <v>0.0015</v>
-      </c>
-      <c r="P15" s="76">
+      <c r="O15" s="46">
+        <v>1.5E-3</v>
+      </c>
+      <c r="P15" s="47">
         <f t="shared" si="1"/>
         <v>1.35</v>
       </c>
-      <c r="Q15" s="133"/>
-      <c r="R15" s="134"/>
-      <c r="S15" s="128"/>
-    </row>
-    <row r="16" s="1" customFormat="1" ht="15.75" spans="1:19">
-      <c r="A16" s="8">
+      <c r="Q15" s="90"/>
+      <c r="R15" s="91"/>
+      <c r="S15" s="85"/>
+    </row>
+    <row r="16" spans="1:34">
+      <c r="A16" s="6">
         <v>14</v>
       </c>
-      <c r="B16" s="35"/>
-      <c r="C16" s="36" t="s">
+      <c r="B16" s="154"/>
+      <c r="C16" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="D16" s="37" t="s">
+      <c r="D16" s="22" t="s">
         <v>105</v>
       </c>
-      <c r="E16" s="37" t="s">
+      <c r="E16" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="F16" s="37" t="s">
+      <c r="F16" s="22" t="s">
         <v>106</v>
       </c>
-      <c r="G16" s="151" t="s">
+      <c r="G16" s="108" t="s">
         <v>33</v>
       </c>
-      <c r="H16" s="38" t="s">
+      <c r="H16" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="I16" s="90"/>
-      <c r="J16" s="91" t="s">
+      <c r="I16" s="111" t="s">
+        <v>26</v>
+      </c>
+      <c r="J16" s="159" t="s">
         <v>108</v>
       </c>
-      <c r="K16" s="92">
+      <c r="K16" s="57">
         <v>500</v>
       </c>
-      <c r="L16" s="37">
+      <c r="L16" s="22">
         <v>1</v>
       </c>
-      <c r="M16" s="18">
+      <c r="M16" s="11">
         <f t="shared" si="0"/>
         <v>400</v>
       </c>
-      <c r="N16" s="93" t="s">
+      <c r="N16" s="58" t="s">
         <v>28</v>
       </c>
-      <c r="O16" s="94">
-        <v>0.0012</v>
-      </c>
-      <c r="P16" s="76">
+      <c r="O16" s="46">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="P16" s="47">
         <f t="shared" si="1"/>
         <v>0.6</v>
       </c>
-      <c r="Q16" s="133"/>
-      <c r="R16" s="134"/>
-      <c r="S16" s="128"/>
-    </row>
-    <row r="17" s="1" customFormat="1" ht="15.75" spans="1:19">
-      <c r="A17" s="8">
+      <c r="Q16" s="90"/>
+      <c r="R16" s="91"/>
+      <c r="S16" s="85"/>
+    </row>
+    <row r="17" spans="1:19">
+      <c r="A17" s="6">
         <v>15</v>
       </c>
-      <c r="B17" s="22"/>
-      <c r="C17" s="156" t="s">
+      <c r="B17" s="153"/>
+      <c r="C17" s="113" t="s">
         <v>109</v>
       </c>
-      <c r="D17" s="157" t="s">
+      <c r="D17" s="114" t="s">
         <v>110</v>
       </c>
-      <c r="E17" s="158" t="s">
+      <c r="E17" s="115" t="s">
         <v>80</v>
       </c>
-      <c r="F17" s="158" t="s">
+      <c r="F17" s="115" t="s">
         <v>111</v>
       </c>
-      <c r="G17" s="159" t="s">
+      <c r="G17" s="116" t="s">
         <v>112</v>
       </c>
-      <c r="H17" s="27" t="s">
+      <c r="H17" s="15" t="s">
         <v>113</v>
       </c>
-      <c r="I17" s="160" t="s">
+      <c r="I17" s="117" t="s">
         <v>26</v>
       </c>
-      <c r="J17" s="158" t="s">
+      <c r="J17" s="115" t="s">
         <v>114</v>
       </c>
-      <c r="K17" s="25">
+      <c r="K17" s="13">
         <v>420</v>
       </c>
-      <c r="L17" s="25">
+      <c r="L17" s="13">
         <v>1</v>
       </c>
-      <c r="M17" s="25">
+      <c r="M17" s="13">
         <f t="shared" si="0"/>
         <v>400</v>
       </c>
-      <c r="N17" s="161" t="s">
+      <c r="N17" s="118" t="s">
         <v>28</v>
       </c>
-      <c r="O17" s="86">
-        <v>0.0138</v>
-      </c>
-      <c r="P17" s="81">
+      <c r="O17" s="54">
+        <v>1.38E-2</v>
+      </c>
+      <c r="P17" s="50">
         <f t="shared" ref="P17:P28" si="2">O17*K17</f>
-        <v>5.796</v>
-      </c>
-      <c r="Q17" s="25"/>
-      <c r="R17" s="131"/>
-      <c r="S17" s="128"/>
-    </row>
-    <row r="18" s="1" customFormat="1" ht="15.75" spans="1:19">
-      <c r="A18" s="8">
+        <v>5.7960000000000003</v>
+      </c>
+      <c r="Q17" s="13"/>
+      <c r="R17" s="88"/>
+      <c r="S17" s="85"/>
+    </row>
+    <row r="18" spans="1:19">
+      <c r="A18" s="6">
         <v>16</v>
       </c>
-      <c r="B18" s="28" t="s">
+      <c r="B18" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="C18" s="171" t="s">
+      <c r="C18" s="128" t="s">
         <v>116</v>
       </c>
-      <c r="D18" s="172" t="s">
+      <c r="D18" s="129" t="s">
         <v>117</v>
       </c>
-      <c r="E18" s="166" t="s">
+      <c r="E18" s="123" t="s">
         <v>118</v>
       </c>
-      <c r="F18" s="166" t="s">
+      <c r="F18" s="123" t="s">
         <v>119</v>
       </c>
-      <c r="G18" s="173" t="s">
+      <c r="G18" s="130" t="s">
         <v>120</v>
       </c>
-      <c r="H18" s="173" t="s">
+      <c r="H18" s="130" t="s">
         <v>26</v>
       </c>
-      <c r="I18" s="166" t="s">
+      <c r="I18" s="123" t="s">
         <v>26</v>
       </c>
-      <c r="J18" s="41"/>
-      <c r="K18" s="41">
+      <c r="J18" s="23"/>
+      <c r="K18" s="23">
         <v>420</v>
       </c>
-      <c r="L18" s="31">
+      <c r="L18" s="17">
         <v>1</v>
       </c>
-      <c r="M18" s="31">
+      <c r="M18" s="17">
         <f t="shared" si="0"/>
         <v>400</v>
       </c>
-      <c r="N18" s="95" t="s">
+      <c r="N18" s="158" t="s">
+        <v>28</v>
+      </c>
+      <c r="O18" s="51">
+        <v>0.05</v>
+      </c>
+      <c r="P18" s="52">
+        <f t="shared" si="2"/>
+        <v>21</v>
+      </c>
+      <c r="Q18" s="17"/>
+      <c r="R18" s="89"/>
+      <c r="S18" s="85"/>
+    </row>
+    <row r="19" spans="1:19">
+      <c r="A19" s="6">
+        <v>17</v>
+      </c>
+      <c r="B19" s="151" t="s">
         <v>121</v>
       </c>
-      <c r="O18" s="83">
-        <v>0.49325</v>
-      </c>
-      <c r="P18" s="84">
+      <c r="C19" s="131" t="s">
+        <v>122</v>
+      </c>
+      <c r="D19" s="132" t="s">
+        <v>123</v>
+      </c>
+      <c r="E19" s="24"/>
+      <c r="F19" s="125" t="s">
+        <v>124</v>
+      </c>
+      <c r="G19" s="9"/>
+      <c r="H19" s="9"/>
+      <c r="I19" s="9"/>
+      <c r="J19" s="9"/>
+      <c r="K19" s="9">
+        <v>410</v>
+      </c>
+      <c r="L19" s="7">
+        <v>1</v>
+      </c>
+      <c r="M19" s="59">
+        <v>400</v>
+      </c>
+      <c r="N19" s="60" t="s">
+        <v>125</v>
+      </c>
+      <c r="O19" s="61">
+        <v>21.26</v>
+      </c>
+      <c r="P19" s="62">
         <f t="shared" si="2"/>
-        <v>207.165</v>
-      </c>
-      <c r="Q18" s="31"/>
-      <c r="R18" s="132">
-        <v>0.441</v>
-      </c>
-      <c r="S18" s="128"/>
-    </row>
-    <row r="19" s="1" customFormat="1" ht="15.75" spans="1:19">
-      <c r="A19" s="8">
-        <v>17</v>
-      </c>
-      <c r="B19" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="C19" s="174" t="s">
-        <v>123</v>
-      </c>
-      <c r="D19" s="175" t="s">
-        <v>124</v>
-      </c>
-      <c r="E19" s="44"/>
-      <c r="F19" s="168" t="s">
-        <v>125</v>
-      </c>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="14"/>
-      <c r="J19" s="14"/>
-      <c r="K19" s="14">
-        <v>920</v>
-      </c>
-      <c r="L19" s="12">
+        <v>8716.6</v>
+      </c>
+      <c r="Q19" s="24"/>
+      <c r="R19" s="84"/>
+      <c r="S19" s="85"/>
+    </row>
+    <row r="20" spans="1:19">
+      <c r="A20" s="6">
+        <v>18</v>
+      </c>
+      <c r="B20" s="152"/>
+      <c r="C20" s="133" t="s">
+        <v>126</v>
+      </c>
+      <c r="D20" s="134" t="s">
+        <v>127</v>
+      </c>
+      <c r="E20" s="111" t="s">
+        <v>128</v>
+      </c>
+      <c r="F20" s="111" t="s">
+        <v>129</v>
+      </c>
+      <c r="G20" s="109" t="s">
+        <v>130</v>
+      </c>
+      <c r="H20" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="I20" s="111" t="s">
+        <v>26</v>
+      </c>
+      <c r="J20" s="109" t="s">
+        <v>63</v>
+      </c>
+      <c r="K20" s="12">
+        <v>420</v>
+      </c>
+      <c r="L20" s="11">
         <v>1</v>
       </c>
-      <c r="M19" s="96">
-        <f>L19*900</f>
-        <v>900</v>
-      </c>
-      <c r="N19" s="97" t="s">
-        <v>126</v>
-      </c>
-      <c r="O19" s="98">
-        <v>21.26</v>
-      </c>
-      <c r="P19" s="99">
-        <f t="shared" si="2"/>
-        <v>19559.2</v>
-      </c>
-      <c r="Q19" s="44"/>
-      <c r="R19" s="127">
-        <v>21.26</v>
-      </c>
-      <c r="S19" s="128"/>
-    </row>
-    <row r="20" s="1" customFormat="1" ht="15.75" spans="1:19">
-      <c r="A20" s="8">
-        <v>18</v>
-      </c>
-      <c r="B20" s="15"/>
-      <c r="C20" s="176" t="s">
-        <v>127</v>
-      </c>
-      <c r="D20" s="177" t="s">
-        <v>128</v>
-      </c>
-      <c r="E20" s="154" t="s">
-        <v>129</v>
-      </c>
-      <c r="F20" s="154" t="s">
-        <v>130</v>
-      </c>
-      <c r="G20" s="152" t="s">
-        <v>131</v>
-      </c>
-      <c r="H20" s="20" t="s">
-        <v>132</v>
-      </c>
-      <c r="I20" s="154" t="s">
-        <v>26</v>
-      </c>
-      <c r="J20" s="152" t="s">
-        <v>63</v>
-      </c>
-      <c r="K20" s="20">
-        <v>420</v>
-      </c>
-      <c r="L20" s="18">
-        <v>1</v>
-      </c>
-      <c r="M20" s="18">
+      <c r="M20" s="11">
         <f t="shared" ref="M20:M28" si="3">L20*400</f>
         <v>400</v>
       </c>
-      <c r="N20" s="100" t="s">
+      <c r="N20" s="63" t="s">
         <v>28</v>
       </c>
-      <c r="O20" s="89">
+      <c r="O20" s="55">
         <v>0.2868</v>
       </c>
-      <c r="P20" s="101">
+      <c r="P20" s="64">
         <f t="shared" si="2"/>
         <v>120.456</v>
       </c>
-      <c r="Q20" s="47"/>
-      <c r="R20" s="129"/>
-      <c r="S20" s="128"/>
-    </row>
-    <row r="21" s="1" customFormat="1" ht="15.75" spans="1:19">
-      <c r="A21" s="8">
+      <c r="Q20" s="25"/>
+      <c r="R20" s="86"/>
+      <c r="S20" s="85"/>
+    </row>
+    <row r="21" spans="1:19">
+      <c r="A21" s="6">
         <v>19</v>
       </c>
-      <c r="B21" s="15"/>
-      <c r="C21" s="176" t="s">
+      <c r="B21" s="152"/>
+      <c r="C21" s="133" t="s">
+        <v>132</v>
+      </c>
+      <c r="D21" s="134" t="s">
         <v>133</v>
       </c>
-      <c r="D21" s="177" t="s">
+      <c r="E21" s="111" t="s">
+        <v>128</v>
+      </c>
+      <c r="F21" s="111" t="s">
         <v>134</v>
       </c>
-      <c r="E21" s="154" t="s">
-        <v>129</v>
-      </c>
-      <c r="F21" s="154" t="s">
+      <c r="G21" s="109" t="s">
         <v>135</v>
       </c>
-      <c r="G21" s="152" t="s">
-        <v>136</v>
-      </c>
-      <c r="H21" s="152" t="s">
+      <c r="H21" s="109" t="s">
         <v>26</v>
       </c>
-      <c r="I21" s="154" t="s">
+      <c r="I21" s="111" t="s">
         <v>26</v>
       </c>
-      <c r="J21" s="152" t="s">
+      <c r="J21" s="109" t="s">
         <v>63</v>
       </c>
-      <c r="K21" s="20">
-        <v>420</v>
-      </c>
-      <c r="L21" s="18">
+      <c r="K21" s="12">
+        <v>410</v>
+      </c>
+      <c r="L21" s="11">
         <v>1</v>
       </c>
-      <c r="M21" s="18">
+      <c r="M21" s="11">
         <f t="shared" si="3"/>
         <v>400</v>
       </c>
-      <c r="N21" s="170" t="s">
+      <c r="N21" s="156" t="s">
+        <v>156</v>
+      </c>
+      <c r="O21" s="65">
+        <v>1.7</v>
+      </c>
+      <c r="P21" s="64">
+        <f>O21*K21</f>
+        <v>697</v>
+      </c>
+      <c r="Q21" s="92"/>
+      <c r="R21" s="86"/>
+      <c r="S21" s="85"/>
+    </row>
+    <row r="22" spans="1:19">
+      <c r="A22" s="6">
+        <v>20</v>
+      </c>
+      <c r="B22" s="153"/>
+      <c r="C22" s="133" t="s">
+        <v>136</v>
+      </c>
+      <c r="D22" s="117" t="s">
         <v>137</v>
       </c>
-      <c r="O21" s="102">
-        <v>5</v>
-      </c>
-      <c r="P21" s="101">
-        <f t="shared" si="2"/>
-        <v>2100</v>
-      </c>
-      <c r="Q21" s="135"/>
-      <c r="R21" s="129">
-        <v>2.756</v>
-      </c>
-      <c r="S21" s="128"/>
-    </row>
-    <row r="22" s="1" customFormat="1" ht="15.75" spans="1:19">
-      <c r="A22" s="8">
-        <v>20</v>
-      </c>
-      <c r="B22" s="22"/>
-      <c r="C22" s="48" t="s">
+      <c r="E22" s="117" t="s">
         <v>138</v>
       </c>
-      <c r="D22" s="160" t="s">
+      <c r="F22" s="27" t="s">
         <v>139</v>
       </c>
-      <c r="E22" s="160" t="s">
+      <c r="G22" s="117" t="s">
         <v>140</v>
       </c>
-      <c r="F22" s="50" t="s">
+      <c r="H22" s="28" t="s">
         <v>141</v>
       </c>
-      <c r="G22" s="160" t="s">
-        <v>142</v>
-      </c>
-      <c r="H22" s="51" t="s">
-        <v>143</v>
-      </c>
-      <c r="I22" s="160" t="s">
+      <c r="I22" s="117" t="s">
         <v>26</v>
       </c>
-      <c r="J22" s="178" t="s">
+      <c r="J22" s="135" t="s">
         <v>63</v>
       </c>
-      <c r="K22" s="27">
+      <c r="K22" s="15">
         <v>420</v>
       </c>
-      <c r="L22" s="25">
+      <c r="L22" s="13">
         <v>1</v>
       </c>
-      <c r="M22" s="25">
+      <c r="M22" s="13">
         <f t="shared" si="3"/>
         <v>400</v>
       </c>
-      <c r="N22" s="103" t="s">
-        <v>28</v>
-      </c>
-      <c r="O22" s="80">
-        <v>0.3607</v>
-      </c>
-      <c r="P22" s="104">
+      <c r="N22" s="157" t="s">
+        <v>156</v>
+      </c>
+      <c r="O22" s="49">
+        <v>0.4</v>
+      </c>
+      <c r="P22" s="66">
         <f t="shared" si="2"/>
-        <v>151.494</v>
-      </c>
-      <c r="Q22" s="49"/>
-      <c r="R22" s="131"/>
-      <c r="S22" s="128"/>
-    </row>
-    <row r="23" s="1" customFormat="1" ht="15.75" spans="1:19">
-      <c r="A23" s="8">
+        <v>168</v>
+      </c>
+      <c r="Q22" s="26"/>
+      <c r="R22" s="88"/>
+      <c r="S22" s="85"/>
+    </row>
+    <row r="23" spans="1:19">
+      <c r="A23" s="6">
         <v>21</v>
       </c>
-      <c r="B23" s="9" t="s">
+      <c r="B23" s="151" t="s">
+        <v>142</v>
+      </c>
+      <c r="C23" s="136" t="s">
+        <v>143</v>
+      </c>
+      <c r="D23" s="137" t="s">
         <v>144</v>
       </c>
-      <c r="C23" s="179" t="s">
+      <c r="E23" s="138" t="s">
+        <v>118</v>
+      </c>
+      <c r="F23" s="138" t="s">
         <v>145</v>
       </c>
-      <c r="D23" s="180" t="s">
-        <v>146</v>
-      </c>
-      <c r="E23" s="181" t="s">
-        <v>118</v>
-      </c>
-      <c r="F23" s="181" t="s">
-        <v>147</v>
-      </c>
-      <c r="G23" s="54"/>
-      <c r="H23" s="55"/>
-      <c r="I23" s="105"/>
-      <c r="J23" s="105"/>
-      <c r="K23" s="105"/>
-      <c r="L23" s="54">
+      <c r="G23" s="29"/>
+      <c r="H23" s="30"/>
+      <c r="I23" s="67"/>
+      <c r="J23" s="67"/>
+      <c r="K23" s="67"/>
+      <c r="L23" s="29">
         <v>1</v>
       </c>
-      <c r="M23" s="54">
+      <c r="M23" s="29">
         <f t="shared" si="3"/>
         <v>400</v>
       </c>
-      <c r="N23" s="106"/>
-      <c r="O23" s="107"/>
-      <c r="P23" s="108">
+      <c r="N23" s="68"/>
+      <c r="O23" s="69"/>
+      <c r="P23" s="70">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q23" s="136"/>
-      <c r="R23" s="137" t="s">
+      <c r="Q23" s="93"/>
+      <c r="R23" s="94" t="s">
+        <v>169</v>
+      </c>
+      <c r="S23" s="85"/>
+    </row>
+    <row r="24" spans="1:19">
+      <c r="A24" s="6">
+        <v>22</v>
+      </c>
+      <c r="B24" s="153"/>
+      <c r="C24" s="139" t="s">
+        <v>146</v>
+      </c>
+      <c r="D24" s="140" t="s">
+        <v>147</v>
+      </c>
+      <c r="E24" s="117" t="s">
+        <v>118</v>
+      </c>
+      <c r="F24" s="117" t="s">
         <v>148</v>
       </c>
-      <c r="S23" s="128"/>
-    </row>
-    <row r="24" s="1" customFormat="1" ht="15.75" spans="1:19">
-      <c r="A24" s="8">
-        <v>22</v>
-      </c>
-      <c r="B24" s="22"/>
-      <c r="C24" s="182" t="s">
-        <v>149</v>
-      </c>
-      <c r="D24" s="183" t="s">
-        <v>150</v>
-      </c>
-      <c r="E24" s="160" t="s">
-        <v>118</v>
-      </c>
-      <c r="F24" s="160" t="s">
-        <v>151</v>
-      </c>
-      <c r="G24" s="49"/>
-      <c r="H24" s="27"/>
-      <c r="I24" s="27"/>
-      <c r="J24" s="27"/>
-      <c r="K24" s="27">
+      <c r="G24" s="26"/>
+      <c r="H24" s="15"/>
+      <c r="I24" s="15"/>
+      <c r="J24" s="15"/>
+      <c r="K24" s="15">
         <v>420</v>
       </c>
-      <c r="L24" s="25">
+      <c r="L24" s="13">
         <v>1</v>
       </c>
-      <c r="M24" s="25">
+      <c r="M24" s="13">
         <f t="shared" si="3"/>
         <v>400</v>
       </c>
-      <c r="N24" s="184" t="s">
+      <c r="N24" s="141" t="s">
+        <v>149</v>
+      </c>
+      <c r="O24" s="71">
+        <v>0.86619999999999997</v>
+      </c>
+      <c r="P24" s="66">
+        <f t="shared" si="2"/>
+        <v>363.80399999999997</v>
+      </c>
+      <c r="Q24" s="95"/>
+      <c r="R24" s="88"/>
+      <c r="S24" s="85"/>
+    </row>
+    <row r="25" spans="1:19">
+      <c r="A25" s="6">
+        <v>23</v>
+      </c>
+      <c r="B25" s="151" t="s">
+        <v>150</v>
+      </c>
+      <c r="C25" s="101" t="s">
+        <v>151</v>
+      </c>
+      <c r="D25" s="102" t="s">
         <v>152</v>
       </c>
-      <c r="O24" s="110">
-        <v>0.8662</v>
-      </c>
-      <c r="P24" s="104">
+      <c r="E25" s="103" t="s">
+        <v>153</v>
+      </c>
+      <c r="F25" s="103" t="s">
+        <v>154</v>
+      </c>
+      <c r="G25" s="103" t="s">
+        <v>155</v>
+      </c>
+      <c r="H25" s="31"/>
+      <c r="I25" s="31"/>
+      <c r="J25" s="7"/>
+      <c r="K25" s="31">
+        <v>35</v>
+      </c>
+      <c r="L25" s="7">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M25" s="31">
+        <f t="shared" si="3"/>
+        <v>35</v>
+      </c>
+      <c r="N25" s="155" t="s">
+        <v>156</v>
+      </c>
+      <c r="O25" s="72">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="P25" s="62">
         <f t="shared" si="2"/>
-        <v>363.804</v>
-      </c>
-      <c r="Q24" s="138"/>
-      <c r="R24" s="131">
-        <v>0.8662</v>
-      </c>
-      <c r="S24" s="128"/>
-    </row>
-    <row r="25" s="1" customFormat="1" ht="15.75" spans="1:19">
-      <c r="A25" s="8">
-        <v>23</v>
-      </c>
-      <c r="B25" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="C25" s="144" t="s">
-        <v>154</v>
-      </c>
-      <c r="D25" s="145" t="s">
+        <v>79.099999999999994</v>
+      </c>
+      <c r="Q25" s="24"/>
+      <c r="R25" s="84"/>
+      <c r="S25" s="85"/>
+    </row>
+    <row r="26" spans="1:19">
+      <c r="A26" s="6">
+        <v>24</v>
+      </c>
+      <c r="B26" s="152"/>
+      <c r="C26" s="106" t="s">
+        <v>157</v>
+      </c>
+      <c r="D26" s="110" t="s">
+        <v>158</v>
+      </c>
+      <c r="E26" s="107" t="s">
+        <v>159</v>
+      </c>
+      <c r="F26" s="107" t="s">
+        <v>159</v>
+      </c>
+      <c r="G26" s="107" t="s">
         <v>155</v>
       </c>
-      <c r="E25" s="146" t="s">
+      <c r="H26" s="32"/>
+      <c r="I26" s="32"/>
+      <c r="J26" s="11"/>
+      <c r="K26" s="32">
+        <v>5</v>
+      </c>
+      <c r="L26" s="11">
+        <v>0.01</v>
+      </c>
+      <c r="M26" s="32">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="N26" s="73" t="s">
         <v>156</v>
       </c>
-      <c r="F25" s="146" t="s">
-        <v>157</v>
-      </c>
-      <c r="G25" s="146" t="s">
-        <v>158</v>
-      </c>
-      <c r="H25" s="58"/>
-      <c r="I25" s="58"/>
-      <c r="J25" s="12"/>
-      <c r="K25" s="58">
-        <v>800</v>
-      </c>
-      <c r="L25" s="12">
-        <v>2</v>
-      </c>
-      <c r="M25" s="58">
-        <f t="shared" si="3"/>
-        <v>800</v>
-      </c>
-      <c r="N25" s="111" t="s">
-        <v>159</v>
-      </c>
-      <c r="O25" s="112">
-        <v>1.74</v>
-      </c>
-      <c r="P25" s="99">
+      <c r="O26" s="55">
+        <v>32.9</v>
+      </c>
+      <c r="P26" s="64">
         <f t="shared" si="2"/>
-        <v>1392</v>
-      </c>
-      <c r="Q25" s="44"/>
-      <c r="R25" s="127"/>
-      <c r="S25" s="128"/>
-    </row>
-    <row r="26" s="1" customFormat="1" ht="15.75" spans="1:19">
-      <c r="A26" s="8">
-        <v>24</v>
-      </c>
-      <c r="B26" s="15"/>
-      <c r="C26" s="149" t="s">
+        <v>164.5</v>
+      </c>
+      <c r="Q26" s="25"/>
+      <c r="R26" s="86"/>
+      <c r="S26" s="85"/>
+    </row>
+    <row r="27" spans="1:19">
+      <c r="A27" s="6">
+        <v>25</v>
+      </c>
+      <c r="B27" s="152"/>
+      <c r="C27" s="142" t="s">
         <v>160</v>
       </c>
-      <c r="D26" s="153" t="s">
+      <c r="D27" s="143" t="s">
         <v>161</v>
       </c>
-      <c r="E26" s="150" t="s">
+      <c r="E27" s="143" t="s">
         <v>162</v>
       </c>
-      <c r="F26" s="150" t="s">
+      <c r="F27" s="33" t="s">
         <v>162</v>
       </c>
-      <c r="G26" s="150" t="s">
-        <v>158</v>
-      </c>
-      <c r="H26" s="59"/>
-      <c r="I26" s="59"/>
-      <c r="J26" s="18"/>
-      <c r="K26" s="59">
-        <v>420</v>
-      </c>
-      <c r="L26" s="18">
-        <v>1</v>
-      </c>
-      <c r="M26" s="59">
-        <f t="shared" si="3"/>
-        <v>400</v>
-      </c>
-      <c r="N26" s="113" t="s">
-        <v>159</v>
-      </c>
-      <c r="O26" s="89">
-        <v>0.329</v>
-      </c>
-      <c r="P26" s="101">
-        <f t="shared" si="2"/>
-        <v>138.18</v>
-      </c>
-      <c r="Q26" s="47"/>
-      <c r="R26" s="129"/>
-      <c r="S26" s="128"/>
-    </row>
-    <row r="27" s="1" customFormat="1" ht="15.75" spans="1:19">
-      <c r="A27" s="8">
-        <v>25</v>
-      </c>
-      <c r="B27" s="15"/>
-      <c r="C27" s="185" t="s">
-        <v>163</v>
-      </c>
-      <c r="D27" s="186" t="s">
-        <v>164</v>
-      </c>
-      <c r="E27" s="186" t="s">
-        <v>165</v>
-      </c>
-      <c r="F27" s="61" t="s">
-        <v>165</v>
-      </c>
-      <c r="G27" s="61"/>
-      <c r="H27" s="61"/>
-      <c r="I27" s="61"/>
-      <c r="J27" s="61"/>
-      <c r="K27" s="61"/>
-      <c r="L27" s="114">
+      <c r="G27" s="33"/>
+      <c r="H27" s="33"/>
+      <c r="I27" s="33"/>
+      <c r="J27" s="33"/>
+      <c r="K27" s="33"/>
+      <c r="L27" s="74">
         <v>5</v>
       </c>
-      <c r="M27" s="114">
+      <c r="M27" s="74">
         <f t="shared" si="3"/>
         <v>2000</v>
       </c>
-      <c r="N27" s="61"/>
-      <c r="O27" s="115"/>
-      <c r="P27" s="116">
+      <c r="N27" s="33"/>
+      <c r="O27" s="75"/>
+      <c r="P27" s="76">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q27" s="139" t="s">
+      <c r="Q27" s="96" t="s">
+        <v>163</v>
+      </c>
+      <c r="R27" s="97"/>
+      <c r="S27" s="85"/>
+    </row>
+    <row r="28" spans="1:19">
+      <c r="A28" s="6">
+        <v>26</v>
+      </c>
+      <c r="B28" s="153"/>
+      <c r="C28" s="144" t="s">
+        <v>164</v>
+      </c>
+      <c r="D28" s="34" t="s">
+        <v>165</v>
+      </c>
+      <c r="E28" s="145" t="s">
         <v>166</v>
       </c>
-      <c r="R27" s="140"/>
-      <c r="S27" s="128"/>
-    </row>
-    <row r="28" s="1" customFormat="1" ht="15.75" spans="1:19">
-      <c r="A28" s="8">
-        <v>26</v>
-      </c>
-      <c r="B28" s="22"/>
-      <c r="C28" s="187" t="s">
-        <v>167</v>
-      </c>
-      <c r="D28" s="63" t="s">
-        <v>168</v>
-      </c>
-      <c r="E28" s="188" t="s">
-        <v>169</v>
-      </c>
-      <c r="F28" s="63" t="s">
-        <v>169</v>
-      </c>
-      <c r="G28" s="63"/>
-      <c r="H28" s="63"/>
-      <c r="I28" s="63"/>
-      <c r="J28" s="63"/>
-      <c r="K28" s="63"/>
-      <c r="L28" s="117">
+      <c r="F28" s="34" t="s">
+        <v>166</v>
+      </c>
+      <c r="G28" s="34"/>
+      <c r="H28" s="34"/>
+      <c r="I28" s="34"/>
+      <c r="J28" s="34"/>
+      <c r="K28" s="34"/>
+      <c r="L28" s="77">
         <v>3</v>
       </c>
-      <c r="M28" s="117">
+      <c r="M28" s="77">
         <f t="shared" si="3"/>
         <v>1200</v>
       </c>
-      <c r="N28" s="63"/>
-      <c r="O28" s="118"/>
-      <c r="P28" s="119">
+      <c r="N28" s="34"/>
+      <c r="O28" s="78"/>
+      <c r="P28" s="79">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q28" s="141" t="s">
-        <v>166</v>
-      </c>
-      <c r="R28" s="142"/>
-      <c r="S28" s="128"/>
-    </row>
-    <row r="29" s="1" customFormat="1" spans="3:19">
-      <c r="C29" s="64"/>
-      <c r="D29" s="65"/>
-      <c r="E29" s="64"/>
-      <c r="G29" s="64"/>
-      <c r="H29" s="64"/>
-      <c r="I29" s="64"/>
-      <c r="J29" s="64"/>
-      <c r="K29" s="64"/>
-      <c r="L29" s="120" t="s">
-        <v>170</v>
-      </c>
-      <c r="M29" s="120"/>
-      <c r="N29" s="120"/>
-      <c r="O29" s="120"/>
-      <c r="P29" s="121">
+      <c r="Q28" s="98" t="s">
+        <v>163</v>
+      </c>
+      <c r="R28" s="99"/>
+      <c r="S28" s="85"/>
+    </row>
+    <row r="29" spans="1:19">
+      <c r="A29" s="1"/>
+      <c r="C29" s="35"/>
+      <c r="D29" s="36"/>
+      <c r="E29" s="35"/>
+      <c r="G29" s="35"/>
+      <c r="H29" s="35"/>
+      <c r="I29" s="35"/>
+      <c r="J29" s="35"/>
+      <c r="K29" s="35"/>
+      <c r="L29" s="148" t="s">
+        <v>167</v>
+      </c>
+      <c r="M29" s="148"/>
+      <c r="N29" s="148"/>
+      <c r="O29" s="148"/>
+      <c r="P29" s="80">
         <f>SUM(P3:P28)</f>
-        <v>24351.264</v>
-      </c>
-      <c r="Q29" s="64"/>
-      <c r="R29" s="64"/>
-      <c r="S29" s="128"/>
-    </row>
-    <row r="30" s="1" customFormat="1" ht="15.75" spans="3:19">
-      <c r="C30" s="64"/>
-      <c r="E30" s="66"/>
-      <c r="F30" s="66"/>
-      <c r="G30" s="64"/>
-      <c r="H30" s="64"/>
-      <c r="I30" s="64"/>
-      <c r="J30" s="64"/>
-      <c r="K30" s="64"/>
-      <c r="L30" s="122" t="s">
-        <v>171</v>
-      </c>
-      <c r="M30" s="123"/>
-      <c r="N30" s="123"/>
-      <c r="O30" s="123"/>
-      <c r="P30" s="124">
+        <v>10649.425000000001</v>
+      </c>
+      <c r="Q29" s="35"/>
+      <c r="R29" s="35"/>
+      <c r="S29" s="85"/>
+    </row>
+    <row r="30" spans="1:19">
+      <c r="A30" s="1"/>
+      <c r="C30" s="35"/>
+      <c r="E30" s="37"/>
+      <c r="F30" s="37"/>
+      <c r="G30" s="35"/>
+      <c r="H30" s="35"/>
+      <c r="I30" s="35"/>
+      <c r="J30" s="35"/>
+      <c r="K30" s="35"/>
+      <c r="L30" s="149" t="s">
+        <v>168</v>
+      </c>
+      <c r="M30" s="150"/>
+      <c r="N30" s="150"/>
+      <c r="O30" s="150"/>
+      <c r="P30" s="81">
         <f>P29/400</f>
-        <v>60.87816</v>
-      </c>
-      <c r="Q30" s="64"/>
-      <c r="R30" s="64"/>
-      <c r="S30" s="128"/>
-    </row>
-    <row r="31" s="1" customFormat="1" spans="4:19">
-      <c r="D31" s="67"/>
-      <c r="E31" s="66"/>
-      <c r="H31" s="2"/>
-      <c r="R31" s="128"/>
-      <c r="S31" s="128"/>
-    </row>
-    <row r="32" s="1" customFormat="1" spans="4:19">
-      <c r="D32" s="66"/>
-      <c r="H32" s="2"/>
-      <c r="R32" s="128"/>
-      <c r="S32" s="128"/>
-    </row>
-    <row r="33" s="1" customFormat="1" spans="3:19">
-      <c r="C33" s="67"/>
-      <c r="D33" s="66"/>
-      <c r="H33" s="2"/>
-      <c r="R33" s="128"/>
-      <c r="S33" s="128"/>
-    </row>
-    <row r="34" s="1" customFormat="1" spans="8:19">
-      <c r="H34" s="2"/>
-      <c r="R34" s="128"/>
-      <c r="S34" s="128"/>
-    </row>
-    <row r="35" s="1" customFormat="1" spans="8:19">
-      <c r="H35" s="2"/>
-      <c r="R35" s="128"/>
-      <c r="S35" s="128"/>
-    </row>
-    <row r="36" s="1" customFormat="1" spans="8:19">
-      <c r="H36" s="2"/>
-      <c r="R36" s="128"/>
-      <c r="S36" s="128"/>
-    </row>
-    <row r="37" s="1" customFormat="1" spans="8:19">
-      <c r="H37" s="2"/>
-      <c r="R37" s="128"/>
-      <c r="S37" s="128"/>
-    </row>
-    <row r="38" s="1" customFormat="1" ht="15.75" customHeight="1" spans="8:19">
-      <c r="H38" s="2"/>
-      <c r="R38" s="128"/>
-      <c r="S38" s="128"/>
-    </row>
-    <row r="39" s="1" customFormat="1" spans="8:19">
-      <c r="H39" s="2"/>
-      <c r="R39" s="128"/>
-      <c r="S39" s="128"/>
-    </row>
-    <row r="40" s="1" customFormat="1" spans="8:19">
-      <c r="H40" s="2"/>
-      <c r="R40" s="128"/>
-      <c r="S40" s="128"/>
-    </row>
-    <row r="41" s="1" customFormat="1" spans="8:19">
-      <c r="H41" s="2"/>
-      <c r="R41" s="128"/>
-      <c r="S41" s="128"/>
-    </row>
-    <row r="42" s="1" customFormat="1" spans="8:19">
-      <c r="H42" s="2"/>
-      <c r="R42" s="128"/>
-      <c r="S42" s="128"/>
-    </row>
-    <row r="43" s="1" customFormat="1" spans="8:19">
-      <c r="H43" s="2"/>
-      <c r="R43" s="128"/>
-      <c r="S43" s="128"/>
-    </row>
-    <row r="44" s="1" customFormat="1" spans="1:17">
-      <c r="A44" s="2"/>
-      <c r="H44" s="68"/>
-      <c r="Q44" s="90"/>
-    </row>
-    <row r="45" s="1" customFormat="1" spans="1:17">
-      <c r="A45" s="2"/>
-      <c r="H45" s="68"/>
-      <c r="Q45" s="90"/>
+        <v>26.623562500000002</v>
+      </c>
+      <c r="Q30" s="35"/>
+      <c r="R30" s="35"/>
+      <c r="S30" s="85"/>
+    </row>
+    <row r="31" spans="1:19">
+      <c r="A31" s="1"/>
+      <c r="D31" s="38"/>
+      <c r="E31" s="37"/>
+      <c r="R31" s="85"/>
+      <c r="S31" s="85"/>
+    </row>
+    <row r="32" spans="1:19">
+      <c r="A32" s="1"/>
+      <c r="D32" s="37"/>
+      <c r="R32" s="85"/>
+      <c r="S32" s="85"/>
+    </row>
+    <row r="33" spans="1:19">
+      <c r="A33" s="1"/>
+      <c r="C33" s="38"/>
+      <c r="D33" s="37"/>
+      <c r="R33" s="85"/>
+      <c r="S33" s="85"/>
+    </row>
+    <row r="34" spans="1:19">
+      <c r="A34" s="1"/>
+      <c r="R34" s="85"/>
+      <c r="S34" s="85"/>
+    </row>
+    <row r="35" spans="1:19">
+      <c r="A35" s="1"/>
+      <c r="R35" s="85"/>
+      <c r="S35" s="85"/>
+    </row>
+    <row r="36" spans="1:19">
+      <c r="A36" s="1"/>
+      <c r="R36" s="85"/>
+      <c r="S36" s="85"/>
+    </row>
+    <row r="37" spans="1:19">
+      <c r="A37" s="1"/>
+      <c r="R37" s="85"/>
+      <c r="S37" s="85"/>
+    </row>
+    <row r="38" spans="1:19" ht="15.75" customHeight="1">
+      <c r="A38" s="1"/>
+      <c r="R38" s="85"/>
+      <c r="S38" s="85"/>
+    </row>
+    <row r="39" spans="1:19">
+      <c r="A39" s="1"/>
+      <c r="R39" s="85"/>
+      <c r="S39" s="85"/>
+    </row>
+    <row r="40" spans="1:19">
+      <c r="A40" s="1"/>
+      <c r="R40" s="85"/>
+      <c r="S40" s="85"/>
+    </row>
+    <row r="41" spans="1:19">
+      <c r="A41" s="1"/>
+      <c r="R41" s="85"/>
+      <c r="S41" s="85"/>
+    </row>
+    <row r="42" spans="1:19">
+      <c r="A42" s="1"/>
+      <c r="R42" s="85"/>
+      <c r="S42" s="85"/>
+    </row>
+    <row r="43" spans="1:19">
+      <c r="A43" s="1"/>
+      <c r="R43" s="85"/>
+      <c r="S43" s="85"/>
+    </row>
+    <row r="44" spans="1:19">
+      <c r="H44" s="39"/>
+      <c r="Q44" s="56"/>
+    </row>
+    <row r="45" spans="1:19">
+      <c r="H45" s="39"/>
+      <c r="Q45" s="56"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -4203,7 +3502,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a7177eaa-5f93-4441-aade-07dbca551305}</x14:id>
+          <x14:id>{A7177EAA-5F93-4441-AADE-07DBCA551305}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4239,7 +3538,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8ae3e078-20bf-4fab-b4d9-9a19e57eb3a1}</x14:id>
+          <x14:id>{8AE3E078-20BF-4FAB-B4D9-9A19E57EB3A1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4265,7 +3564,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{73c16a20-6ca5-41f8-8719-298c2c627fbf}</x14:id>
+          <x14:id>{73C16A20-6CA5-41F8-8719-298C2C627FBF}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4279,7 +3578,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a8943134-f8f0-4df3-a9a0-86442e65814b}</x14:id>
+          <x14:id>{A8943134-F8F0-4DF3-A9A0-86442E65814B}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4305,7 +3604,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{73d72061-44be-43bf-b86a-016273a3fadd}</x14:id>
+          <x14:id>{73D72061-44BE-43BF-B86A-016273A3FADD}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4319,7 +3618,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{431abf7b-01d1-4562-b5f9-4f47436b3001}</x14:id>
+          <x14:id>{431ABF7B-01D1-4562-B5F9-4F47436B3001}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4333,7 +3632,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2d34257c-d5c6-42a5-a089-b74c0971175c}</x14:id>
+          <x14:id>{2D34257C-D5C6-42A5-A089-B74C0971175C}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4347,7 +3646,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{70ce0387-edb2-443c-842f-1d5ee6e70af7}</x14:id>
+          <x14:id>{70CE0387-EDB2-443C-842F-1D5EE6E70AF7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4389,35 +3688,34 @@
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="N3" r:id="rId1" display="LCSC"/>
-    <hyperlink ref="N4" r:id="rId2" display="LCSC"/>
-    <hyperlink ref="N5" r:id="rId3" display="LCSC"/>
-    <hyperlink ref="N8" r:id="rId4" display="LCSC"/>
-    <hyperlink ref="N9" r:id="rId5" display="LCSC"/>
-    <hyperlink ref="N10" r:id="rId6" display="LCSC"/>
-    <hyperlink ref="N11" r:id="rId7" display="LCSC"/>
-    <hyperlink ref="N13" r:id="rId8" display="LCSC"/>
-    <hyperlink ref="N12" r:id="rId9" display="LCSC"/>
-    <hyperlink ref="N14" r:id="rId10" display="LCSC"/>
-    <hyperlink ref="N17" r:id="rId11" display="LCSC"/>
-    <hyperlink ref="N18" r:id="rId12" display="Utsource"/>
-    <hyperlink ref="N20" r:id="rId13" display="LCSC"/>
-    <hyperlink ref="N6" r:id="rId14" display="LCSC"/>
-    <hyperlink ref="N7" r:id="rId15" display="LCSC"/>
-    <hyperlink ref="N21" r:id="rId16" display="Alibaba"/>
-    <hyperlink ref="N25" r:id="rId17" display="Aliexpress"/>
-    <hyperlink ref="N26" r:id="rId18" display="Aliexpress"/>
-    <hyperlink ref="N22" r:id="rId19" display="LCSC"/>
-    <hyperlink ref="N15" r:id="rId20" display="LCSC"/>
-    <hyperlink ref="N16" r:id="rId21" display="LCSC"/>
+    <hyperlink ref="N3" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="N4" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="N5" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="N8" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="N9" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="N10" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="N11" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="N13" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="N12" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="N14" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="N17" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="N18" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="N20" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="N6" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="N7" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="N21" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="N25" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="N26" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="N22" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="N15" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="N16" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a7177eaa-5f93-4441-aade-07dbca551305}">
+          <x14:cfRule type="dataBar" id="{A7177EAA-5F93-4441-AADE-07DBCA551305}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -4430,7 +3728,7 @@
           <xm:sqref>Q24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8ae3e078-20bf-4fab-b4d9-9a19e57eb3a1}">
+          <x14:cfRule type="dataBar" id="{8AE3E078-20BF-4FAB-B4D9-9A19E57EB3A1}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -4443,7 +3741,7 @@
           <xm:sqref>Q27</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{73c16a20-6ca5-41f8-8719-298c2c627fbf}">
+          <x14:cfRule type="dataBar" id="{73C16A20-6CA5-41F8-8719-298C2C627FBF}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -4456,7 +3754,7 @@
           <xm:sqref>Q28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a8943134-f8f0-4df3-a9a0-86442e65814b}">
+          <x14:cfRule type="dataBar" id="{A8943134-F8F0-4DF3-A9A0-86442E65814B}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -4469,7 +3767,7 @@
           <xm:sqref>P30</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{73d72061-44be-43bf-b86a-016273a3fadd}">
+          <x14:cfRule type="dataBar" id="{73D72061-44BE-43BF-B86A-016273A3FADD}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -4482,7 +3780,7 @@
           <xm:sqref>N3:N5</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{431abf7b-01d1-4562-b5f9-4f47436b3001}">
+          <x14:cfRule type="dataBar" id="{431ABF7B-01D1-4562-B5F9-4F47436B3001}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -4495,7 +3793,7 @@
           <xm:sqref>N9:N10</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2d34257c-d5c6-42a5-a089-b74c0971175c}">
+          <x14:cfRule type="dataBar" id="{2D34257C-D5C6-42A5-A089-B74C0971175C}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -4508,7 +3806,7 @@
           <xm:sqref>N18:N20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{70ce0387-edb2-443c-842f-1d5ee6e70af7}">
+          <x14:cfRule type="dataBar" id="{70CE0387-EDB2-443C-842F-1D5EE6E70AF7}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
